--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0010_ses-01_WMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0010_ses-01_WMprob_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -628,7 +629,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="0">
-        <v>0</v>
+        <v>0.0019860578737264439</v>
       </c>
       <c r="J15" s="0">
         <v>0</v>
@@ -648,7 +649,7 @@
         <v>0</v>
       </c>
       <c r="C16" s="0">
-        <v>0</v>
+        <v>0.001268086077682952</v>
       </c>
       <c r="D16" s="0">
         <v>0</v>
@@ -660,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="0">
-        <v>0</v>
+        <v>0.020116676725005011</v>
       </c>
       <c r="H16" s="0">
         <v>0</v>
@@ -669,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="0">
-        <v>0</v>
+        <v>0.018402649981597335</v>
       </c>
       <c r="K16" s="0">
         <v>0</v>
@@ -680,19 +681,19 @@
     </row>
     <row r="17">
       <c r="A17" s="0">
-        <v>0</v>
+        <v>0.0073840700994388039</v>
       </c>
       <c r="B17" s="0">
         <v>0</v>
       </c>
       <c r="C17" s="0">
-        <v>0</v>
+        <v>0.0038042582330488559</v>
       </c>
       <c r="D17" s="0">
-        <v>0</v>
+        <v>0.004808501430529172</v>
       </c>
       <c r="E17" s="0">
-        <v>0</v>
+        <v>0.0005966765118291113</v>
       </c>
       <c r="F17" s="0">
         <v>0</v>
@@ -718,28 +719,28 @@
     </row>
     <row r="18">
       <c r="A18" s="0">
-        <v>0</v>
+        <v>0.0049227133996258832</v>
       </c>
       <c r="B18" s="0">
         <v>0</v>
       </c>
       <c r="C18" s="0">
-        <v>0</v>
+        <v>0.011412774699146599</v>
       </c>
       <c r="D18" s="0">
-        <v>0</v>
+        <v>0.0096170028610583699</v>
       </c>
       <c r="E18" s="0">
-        <v>0</v>
+        <v>0.00059667651182911303</v>
       </c>
       <c r="F18" s="0">
-        <v>0</v>
+        <v>0.0036386129607393729</v>
       </c>
       <c r="G18" s="0">
-        <v>0</v>
+        <v>0.040233353450010133</v>
       </c>
       <c r="H18" s="0">
-        <v>0</v>
+        <v>0.017042549565415018</v>
       </c>
       <c r="I18" s="0">
         <v>0</v>
@@ -748,7 +749,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="0">
-        <v>0</v>
+        <v>0.12886597938144354</v>
       </c>
       <c r="L18" s="0">
         <v>0</v>
@@ -756,34 +757,34 @@
     </row>
     <row r="19">
       <c r="A19" s="0">
-        <v>0</v>
+        <v>0.014768140198877608</v>
       </c>
       <c r="B19" s="0">
         <v>0</v>
       </c>
       <c r="C19" s="0">
-        <v>0</v>
+        <v>0.019021291165244279</v>
       </c>
       <c r="D19" s="0">
-        <v>0</v>
+        <v>0.028851008583175027</v>
       </c>
       <c r="E19" s="0">
-        <v>0.0023867060473164452</v>
+        <v>0.0047734120946328904</v>
       </c>
       <c r="F19" s="0">
-        <v>0.0018193064803696812</v>
+        <v>0.0036386129607393625</v>
       </c>
       <c r="G19" s="0">
-        <v>0</v>
+        <v>0.14081673707503506</v>
       </c>
       <c r="H19" s="0">
-        <v>0</v>
+        <v>0.017042549565414972</v>
       </c>
       <c r="I19" s="0">
-        <v>0.0019860578737264387</v>
+        <v>0.0079442314949057548</v>
       </c>
       <c r="J19" s="0">
-        <v>0.018402649981597335</v>
+        <v>0</v>
       </c>
       <c r="K19" s="0">
         <v>0.12886597938144317</v>
@@ -794,1481 +795,1481 @@
     </row>
     <row r="20">
       <c r="A20" s="0">
-        <v>0.0049227133996258693</v>
+        <v>0.06891798759476217</v>
       </c>
       <c r="B20" s="0">
         <v>0</v>
       </c>
       <c r="C20" s="0">
-        <v>0</v>
+        <v>0.034238324097439703</v>
       </c>
       <c r="D20" s="0">
-        <v>0</v>
+        <v>0.076936022888466751</v>
       </c>
       <c r="E20" s="0">
-        <v>0.0083534711656075584</v>
+        <v>0.011336853724753116</v>
       </c>
       <c r="F20" s="0">
-        <v>0.0036386129607393625</v>
+        <v>0.02365098424480586</v>
       </c>
       <c r="G20" s="0">
-        <v>0.020116676725005011</v>
+        <v>0.32186682760008018</v>
       </c>
       <c r="H20" s="0">
-        <v>0.017042549565414972</v>
+        <v>0.045446798841106584</v>
       </c>
       <c r="I20" s="0">
-        <v>0.0079442314949057548</v>
+        <v>0.01588846298981151</v>
       </c>
       <c r="J20" s="0">
-        <v>0</v>
+        <v>0.018402649981597335</v>
       </c>
       <c r="K20" s="0">
         <v>0.12886597938144317</v>
       </c>
       <c r="L20" s="0">
-        <v>0.0031101296924081708</v>
+        <v>0.010885453923428597</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>0.0024613566998129416</v>
+        <v>0.16983361228709296</v>
       </c>
       <c r="B21" s="0">
-        <v>0</v>
+        <v>0.087719298245614197</v>
       </c>
       <c r="C21" s="0">
-        <v>0.0012680860776829556</v>
+        <v>0.13061286600134442</v>
       </c>
       <c r="D21" s="0">
-        <v>0</v>
+        <v>0.19714855865169656</v>
       </c>
       <c r="E21" s="0">
-        <v>0.014916912795727825</v>
+        <v>0.031027178615113872</v>
       </c>
       <c r="F21" s="0">
-        <v>0.012735145362587807</v>
+        <v>0.078230178655896515</v>
       </c>
       <c r="G21" s="0">
-        <v>0</v>
+        <v>0.32186682760008106</v>
       </c>
       <c r="H21" s="0">
-        <v>0.0056808498551383394</v>
+        <v>0.18178719536442686</v>
       </c>
       <c r="I21" s="0">
-        <v>0.013902405116085108</v>
+        <v>0.05163750471688755</v>
       </c>
       <c r="J21" s="0">
-        <v>0</v>
+        <v>0.05520794994479216</v>
       </c>
       <c r="K21" s="0">
-        <v>0</v>
+        <v>0.25773195876288707</v>
       </c>
       <c r="L21" s="0">
-        <v>0.006220259384816359</v>
+        <v>0.018660778154449075</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0">
-        <v>0.017229496898690543</v>
+        <v>0.30520823077680392</v>
       </c>
       <c r="B22" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C22" s="0">
-        <v>0.0088766025437806654</v>
+        <v>0.30180448648854258</v>
       </c>
       <c r="D22" s="0">
-        <v>0.002404250715264586</v>
+        <v>0.46642463876132961</v>
       </c>
       <c r="E22" s="0">
-        <v>0.059667651182911133</v>
+        <v>0.095468241892657818</v>
       </c>
       <c r="F22" s="0">
-        <v>0.038205436087763313</v>
+        <v>0.17829203507622879</v>
       </c>
       <c r="G22" s="0">
-        <v>0.020116676725005011</v>
+        <v>1.3679340173003409</v>
       </c>
       <c r="H22" s="0">
-        <v>0.073851048116798199</v>
+        <v>0.23291484406067128</v>
       </c>
       <c r="I22" s="0">
-        <v>0.051637504716887404</v>
+        <v>0.12114953029731276</v>
       </c>
       <c r="J22" s="0">
-        <v>0.03680529996319467</v>
+        <v>0.25763709974236265</v>
       </c>
       <c r="K22" s="0">
-        <v>0.12886597938144317</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L22" s="0">
-        <v>0.013995583615836769</v>
+        <v>0.052872204770938902</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>0.039381707197006954</v>
+        <v>0.57841882445603965</v>
       </c>
       <c r="B23" s="0">
-        <v>0.26315789473684187</v>
+        <v>0.87719298245613953</v>
       </c>
       <c r="C23" s="0">
-        <v>0.015217032932195423</v>
+        <v>0.62389835022001239</v>
       </c>
       <c r="D23" s="0">
-        <v>0.016829755006852101</v>
+        <v>0.92563652537686547</v>
       </c>
       <c r="E23" s="0">
-        <v>0.13484889167337916</v>
+        <v>0.19391986634446118</v>
       </c>
       <c r="F23" s="0">
-        <v>0.081868791616635669</v>
+        <v>0.32929447294691233</v>
       </c>
       <c r="G23" s="0">
-        <v>0.060350030175015036</v>
+        <v>1.589217461275396</v>
       </c>
       <c r="H23" s="0">
-        <v>0.15906379594387307</v>
+        <v>0.46014883826620417</v>
       </c>
       <c r="I23" s="0">
-        <v>0.15888462989811508</v>
+        <v>0.25818752358443703</v>
       </c>
       <c r="J23" s="0">
-        <v>0.018402649981597335</v>
+        <v>0.62569009937430942</v>
       </c>
       <c r="K23" s="0">
-        <v>0.64432989690721587</v>
+        <v>1.0309278350515454</v>
       </c>
       <c r="L23" s="0">
-        <v>0.055982334463347078</v>
+        <v>0.15395141977420446</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0">
-        <v>0.17229496898690591</v>
+        <v>1.016540317022745</v>
       </c>
       <c r="B24" s="0">
-        <v>0.61403508771929938</v>
+        <v>1.2280701754385988</v>
       </c>
       <c r="C24" s="0">
-        <v>0.036774496252805711</v>
+        <v>1.0322220672339257</v>
       </c>
       <c r="D24" s="0">
-        <v>0.045680763590027255</v>
+        <v>1.639698987810452</v>
       </c>
       <c r="E24" s="0">
-        <v>0.27208448939407553</v>
+        <v>0.38783973268892341</v>
       </c>
       <c r="F24" s="0">
-        <v>0.16009897027253239</v>
+        <v>0.64949241349197817</v>
       </c>
       <c r="G24" s="0">
-        <v>0.28163347415007095</v>
+        <v>2.5145845906256335</v>
       </c>
       <c r="H24" s="0">
-        <v>0.29540419246719363</v>
+        <v>1.1929784695790513</v>
       </c>
       <c r="I24" s="0">
-        <v>0.27010387082679638</v>
+        <v>0.55411014676967796</v>
       </c>
       <c r="J24" s="0">
-        <v>0.20242914979757123</v>
+        <v>1.0121457489878563</v>
       </c>
       <c r="K24" s="0">
-        <v>1.159793814432992</v>
+        <v>3.0927835051546451</v>
       </c>
       <c r="L24" s="0">
-        <v>0.18505271669828666</v>
+        <v>0.33589400678008335</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>0.22644481638278999</v>
+        <v>1.7623313970660615</v>
       </c>
       <c r="B25" s="0">
-        <v>1.3157894736842093</v>
+        <v>1.5789473684210513</v>
       </c>
       <c r="C25" s="0">
-        <v>0.13314903815670995</v>
+        <v>1.6180778351234468</v>
       </c>
       <c r="D25" s="0">
-        <v>0.096170028610583422</v>
+        <v>2.4956122424446399</v>
       </c>
       <c r="E25" s="0">
-        <v>0.53581550762254193</v>
+        <v>0.70885169605298426</v>
       </c>
       <c r="F25" s="0">
-        <v>0.46028453953352938</v>
+        <v>1.131608630789942</v>
       </c>
       <c r="G25" s="0">
-        <v>0.38221685777509523</v>
+        <v>3.4600683967008616</v>
       </c>
       <c r="H25" s="0">
-        <v>0.55672328580355568</v>
+        <v>1.8860421519059236</v>
       </c>
       <c r="I25" s="0">
-        <v>0.5997894778653845</v>
+        <v>1.0367222100852009</v>
       </c>
       <c r="J25" s="0">
-        <v>0.47846889952153066</v>
+        <v>1.8402649981597332</v>
       </c>
       <c r="K25" s="0">
-        <v>3.2216494845360795</v>
+        <v>4.510309278350511</v>
       </c>
       <c r="L25" s="0">
-        <v>0.35921997947314371</v>
+        <v>0.67178801356016493</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0">
-        <v>0.57841882445603965</v>
+        <v>2.4072068524170498</v>
       </c>
       <c r="B26" s="0">
-        <v>1.8421052631578929</v>
+        <v>2.5438596491228047</v>
       </c>
       <c r="C26" s="0">
-        <v>0.31828960549842095</v>
+        <v>2.5260274667444405</v>
       </c>
       <c r="D26" s="0">
-        <v>0.22840381795013565</v>
+        <v>3.7121631043685204</v>
       </c>
       <c r="E26" s="0">
-        <v>0.8956114442554961</v>
+        <v>1.2416838211163805</v>
       </c>
       <c r="F26" s="0">
-        <v>0.78048248007859333</v>
+        <v>1.7574500600371123</v>
       </c>
       <c r="G26" s="0">
-        <v>1.1265338966002805</v>
+        <v>4.3854355260510927</v>
       </c>
       <c r="H26" s="0">
-        <v>1.1645742203033562</v>
+        <v>2.4541271374197558</v>
       </c>
       <c r="I26" s="0">
-        <v>1.1777323191197782</v>
+        <v>1.6603443824353028</v>
       </c>
       <c r="J26" s="0">
-        <v>1.0121457489878534</v>
+        <v>2.649981597350016</v>
       </c>
       <c r="K26" s="0">
-        <v>3.9948453608247383</v>
+        <v>7.4742268041237043</v>
       </c>
       <c r="L26" s="0">
-        <v>0.68111840263738943</v>
+        <v>1.132087208036574</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>0.90577926553115995</v>
+        <v>3.0028551737717804</v>
       </c>
       <c r="B27" s="0">
-        <v>2.2807017543859631</v>
+        <v>5.6140350877192935</v>
       </c>
       <c r="C27" s="0">
-        <v>0.60741323121013402</v>
+        <v>3.3464791590053102</v>
       </c>
       <c r="D27" s="0">
-        <v>0.48565864448344631</v>
+        <v>4.693097396196471</v>
       </c>
       <c r="E27" s="0">
-        <v>1.543602136101911</v>
+        <v>1.8586473343476817</v>
       </c>
       <c r="F27" s="0">
-        <v>1.3080813593858009</v>
+        <v>2.5834152021249479</v>
       </c>
       <c r="G27" s="0">
-        <v>1.5489841078253859</v>
+        <v>4.6871856769261679</v>
       </c>
       <c r="H27" s="0">
-        <v>1.880361302050785</v>
+        <v>3.4028290632278555</v>
       </c>
       <c r="I27" s="0">
-        <v>1.7318424658894545</v>
+        <v>2.35347858036583</v>
       </c>
       <c r="J27" s="0">
-        <v>1.3986013986013974</v>
+        <v>3.956569746043427</v>
       </c>
       <c r="K27" s="0">
-        <v>7.7319587628865918</v>
+        <v>8.6340206185566935</v>
       </c>
       <c r="L27" s="0">
-        <v>1.2067303206543702</v>
+        <v>1.9329456038316781</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>1.5900364280791557</v>
+        <v>3.7117259033179058</v>
       </c>
       <c r="B28" s="0">
-        <v>5.7017543859649065</v>
+        <v>5.4385964912280658</v>
       </c>
       <c r="C28" s="0">
-        <v>1.0474391001661183</v>
+        <v>3.933603012972517</v>
       </c>
       <c r="D28" s="0">
-        <v>0.98574279325848013</v>
+        <v>5.474478878657461</v>
       </c>
       <c r="E28" s="0">
-        <v>2.1611623258450412</v>
+        <v>2.4690474059488623</v>
       </c>
       <c r="F28" s="0">
-        <v>2.0940217589055035</v>
+        <v>3.2729323581850571</v>
       </c>
       <c r="G28" s="0">
-        <v>2.5145845906256263</v>
+        <v>5.009052504526248</v>
       </c>
       <c r="H28" s="0">
-        <v>2.669999431915012</v>
+        <v>4.2947224904845731</v>
       </c>
       <c r="I28" s="0">
-        <v>2.599749756707908</v>
+        <v>3.2452185656690009</v>
       </c>
       <c r="J28" s="0">
-        <v>2.4107471475892508</v>
+        <v>4.3246227456753736</v>
       </c>
       <c r="K28" s="0">
-        <v>8.376288659793806</v>
+        <v>9.6649484536082397</v>
       </c>
       <c r="L28" s="0">
-        <v>1.875408204522127</v>
+        <v>2.7431343887040067</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>2.5056611204095813</v>
+        <v>3.85694594860689</v>
       </c>
       <c r="B29" s="0">
-        <v>5.8771929824561679</v>
+        <v>7.8070175438596863</v>
       </c>
       <c r="C29" s="0">
-        <v>1.7081119466389456</v>
+        <v>4.5169226087067003</v>
       </c>
       <c r="D29" s="0">
-        <v>1.6228692328036041</v>
+        <v>5.7726059673503016</v>
       </c>
       <c r="E29" s="0">
-        <v>2.76977236791075</v>
+        <v>3.0531937110295795</v>
       </c>
       <c r="F29" s="0">
-        <v>2.7726230760834101</v>
+        <v>3.995197030891843</v>
       </c>
       <c r="G29" s="0">
-        <v>3.2790183061758351</v>
+        <v>4.304968819151096</v>
       </c>
       <c r="H29" s="0">
-        <v>3.4596375617792581</v>
+        <v>4.7435096290405268</v>
       </c>
       <c r="I29" s="0">
-        <v>3.3802705010824177</v>
+        <v>4.1091537407400241</v>
       </c>
       <c r="J29" s="0">
-        <v>3.2388663967611486</v>
+        <v>4.931910195068113</v>
       </c>
       <c r="K29" s="0">
-        <v>9.664948453608293</v>
+        <v>11.984536082474284</v>
       </c>
       <c r="L29" s="0">
-        <v>2.6871520542406744</v>
+        <v>3.3667153920318636</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>2.8502510583833782</v>
+        <v>3.8569459486068687</v>
       </c>
       <c r="B30" s="0">
-        <v>7.2807017543859587</v>
+        <v>6.1403508771929767</v>
       </c>
       <c r="C30" s="0">
-        <v>2.6084530617938322</v>
+        <v>4.612029064532897</v>
       </c>
       <c r="D30" s="0">
-        <v>2.5557185103262547</v>
+        <v>5.8495419902387367</v>
       </c>
       <c r="E30" s="0">
-        <v>3.4285032369700739</v>
+        <v>3.5890092186521043</v>
       </c>
       <c r="F30" s="0">
-        <v>3.4512243932612856</v>
+        <v>4.2153331150165521</v>
       </c>
       <c r="G30" s="0">
-        <v>4.0836853751760174</v>
+        <v>3.6612351639509124</v>
       </c>
       <c r="H30" s="0">
-        <v>4.3685735386013702</v>
+        <v>4.2379139919331896</v>
       </c>
       <c r="I30" s="0">
-        <v>4.0257393100434911</v>
+        <v>4.6870965819943953</v>
       </c>
       <c r="J30" s="0">
-        <v>4.1405962458593999</v>
+        <v>4.6926757453073202</v>
       </c>
       <c r="K30" s="0">
-        <v>10.95360824742267</v>
+        <v>12.113402061855659</v>
       </c>
       <c r="L30" s="0">
-        <v>3.4180325319565794</v>
+        <v>3.8643361428171521</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>3.5886580683272586</v>
+        <v>3.8397164517081777</v>
       </c>
       <c r="B31" s="0">
-        <v>7.1052631578947301</v>
+        <v>6.9298245614035023</v>
       </c>
       <c r="C31" s="0">
-        <v>3.3261897817623836</v>
+        <v>4.5955439455230183</v>
       </c>
       <c r="D31" s="0">
-        <v>3.8443968937080726</v>
+        <v>5.0489265020556298</v>
       </c>
       <c r="E31" s="0">
-        <v>3.7095378740415854</v>
+        <v>3.8533369133924009</v>
       </c>
       <c r="F31" s="0">
-        <v>4.2044172761343335</v>
+        <v>4.2426227122220972</v>
       </c>
       <c r="G31" s="0">
-        <v>4.9487024743512329</v>
+        <v>3.3796016898008419</v>
       </c>
       <c r="H31" s="0">
-        <v>4.7889564278816072</v>
+        <v>3.9822757484519644</v>
       </c>
       <c r="I31" s="0">
-        <v>4.6573057138884986</v>
+        <v>4.8122182280391614</v>
       </c>
       <c r="J31" s="0">
-        <v>4.987118145012877</v>
+        <v>5.4287817445712134</v>
       </c>
       <c r="K31" s="0">
-        <v>11.082474226804113</v>
+        <v>7.8608247422680337</v>
       </c>
       <c r="L31" s="0">
-        <v>4.0571641837464592</v>
+        <v>4.2017852144434391</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>3.9652456433986378</v>
+        <v>3.5640445013291293</v>
       </c>
       <c r="B32" s="0">
-        <v>6.9298245614035023</v>
+        <v>5.6140350877192935</v>
       </c>
       <c r="C32" s="0">
-        <v>4.0058839194004454</v>
+        <v>4.3901140009383797</v>
       </c>
       <c r="D32" s="0">
-        <v>4.8421609405428754</v>
+        <v>4.5247998461279497</v>
       </c>
       <c r="E32" s="0">
-        <v>3.8378233240848436</v>
+        <v>3.9488051552850587</v>
       </c>
       <c r="F32" s="0">
-        <v>4.0952588873121529</v>
+        <v>4.1935014372521158</v>
       </c>
       <c r="G32" s="0">
-        <v>4.8682357674512131</v>
+        <v>3.0778515389257666</v>
       </c>
       <c r="H32" s="0">
-        <v>4.3742543884565093</v>
+        <v>3.5675737090268669</v>
       </c>
       <c r="I32" s="0">
-        <v>4.8996047744831248</v>
+        <v>4.8281066910289718</v>
       </c>
       <c r="J32" s="0">
-        <v>5.2815605447184346</v>
+        <v>4.103790945896205</v>
       </c>
       <c r="K32" s="0">
-        <v>9.4072164948453523</v>
+        <v>7.6030927835051472</v>
       </c>
       <c r="L32" s="0">
-        <v>4.2111156035206632</v>
+        <v>4.2468820949833566</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>3.911095796002753</v>
+        <v>3.4458993797381088</v>
       </c>
       <c r="B33" s="0">
-        <v>5.0877192982456094</v>
+        <v>4.122807017543856</v>
       </c>
       <c r="C33" s="0">
-        <v>4.4421055301233805</v>
+        <v>4.1364967854017891</v>
       </c>
       <c r="D33" s="0">
-        <v>5.5345851465390759</v>
+        <v>3.447695525689416</v>
       </c>
       <c r="E33" s="0">
-        <v>3.9010710343387296</v>
+        <v>3.844386765714964</v>
       </c>
       <c r="F33" s="0">
-        <v>4.2899246807117084</v>
+        <v>3.9224247716770333</v>
       </c>
       <c r="G33" s="0">
-        <v>4.4860189096761172</v>
+        <v>2.9571514785757369</v>
       </c>
       <c r="H33" s="0">
-        <v>3.8857013009146133</v>
+        <v>3.1017440209055245</v>
       </c>
       <c r="I33" s="0">
-        <v>4.7288037973426507</v>
+        <v>4.6116263827927906</v>
       </c>
       <c r="J33" s="0">
-        <v>4.913507545086488</v>
+        <v>3.5149061464850906</v>
       </c>
       <c r="K33" s="0">
-        <v>6.8298969072164883</v>
+        <v>4.1237113402061816</v>
       </c>
       <c r="L33" s="0">
-        <v>4.2935340403694795</v>
+        <v>4.2904239106770721</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0">
-        <v>3.6748055528207115</v>
+        <v>3.5345082209313743</v>
       </c>
       <c r="B34" s="0">
-        <v>4.122807017543856</v>
+        <v>3.2456140350877161</v>
       </c>
       <c r="C34" s="0">
-        <v>4.620905667076677</v>
+        <v>3.915849807884956</v>
       </c>
       <c r="D34" s="0">
-        <v>5.8327122352318845</v>
+        <v>3.0485899069554945</v>
       </c>
       <c r="E34" s="0">
-        <v>3.7119245800889011</v>
+        <v>3.6958143142695157</v>
       </c>
       <c r="F34" s="0">
-        <v>4.0461376123421715</v>
+        <v>3.6477094931412113</v>
       </c>
       <c r="G34" s="0">
-        <v>3.9629853148259877</v>
+        <v>2.9772681553007416</v>
       </c>
       <c r="H34" s="0">
-        <v>3.4255524626484095</v>
+        <v>2.6984036811907037</v>
       </c>
       <c r="I34" s="0">
-        <v>4.6573057138884986</v>
+        <v>4.3832297273142507</v>
       </c>
       <c r="J34" s="0">
-        <v>4.6190651453809313</v>
+        <v>3.1100478468899495</v>
       </c>
       <c r="K34" s="0">
-        <v>4.8969072164948413</v>
+        <v>2.7061855670103068</v>
       </c>
       <c r="L34" s="0">
-        <v>4.2733181973688268</v>
+        <v>3.9949615898982951</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0">
-        <v>3.4852810869351347</v>
+        <v>3.2932952643497253</v>
       </c>
       <c r="B35" s="0">
-        <v>3.0701754385965052</v>
+        <v>2.8070175438596623</v>
       </c>
       <c r="C35" s="0">
-        <v>4.4877566289199926</v>
+        <v>3.6685730227368003</v>
       </c>
       <c r="D35" s="0">
-        <v>5.7100954487534228</v>
+        <v>2.7865265789916704</v>
       </c>
       <c r="E35" s="0">
-        <v>3.6844774605447825</v>
+        <v>3.6415167516930866</v>
       </c>
       <c r="F35" s="0">
-        <v>4.0006549503329518</v>
+        <v>3.649528799621601</v>
       </c>
       <c r="G35" s="0">
-        <v>3.4600683967008807</v>
+        <v>2.9772681553007585</v>
       </c>
       <c r="H35" s="0">
-        <v>3.0449355223541583</v>
+        <v>2.4427654377094927</v>
       </c>
       <c r="I35" s="0">
-        <v>4.325634048976208</v>
+        <v>4.2422196182796963</v>
       </c>
       <c r="J35" s="0">
-        <v>3.533308796466708</v>
+        <v>2.5947736474052387</v>
       </c>
       <c r="K35" s="0">
-        <v>2.9639175257732098</v>
+        <v>1.4175257731958828</v>
       </c>
       <c r="L35" s="0">
-        <v>3.9280938015115412</v>
+        <v>3.7663670575063155</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>3.3523678251452171</v>
+        <v>3.3302156148469004</v>
       </c>
       <c r="B36" s="0">
-        <v>2.7192982456140329</v>
+        <v>1.5789473684210513</v>
       </c>
       <c r="C36" s="0">
-        <v>4.4104033781813072</v>
+        <v>3.4517303034529952</v>
       </c>
       <c r="D36" s="0">
-        <v>5.0272882456182488</v>
+        <v>2.9259731204770008</v>
       </c>
       <c r="E36" s="0">
-        <v>3.4947343297831046</v>
+        <v>3.5370983621229719</v>
       </c>
       <c r="F36" s="0">
-        <v>3.7186624458756286</v>
+        <v>3.3493432303605837</v>
       </c>
       <c r="G36" s="0">
-        <v>3.1382015691007821</v>
+        <v>2.8968014484007214</v>
       </c>
       <c r="H36" s="0">
-        <v>2.5450207351019691</v>
+        <v>2.2837016417656062</v>
       </c>
       <c r="I36" s="0">
-        <v>4.2958431808702873</v>
+        <v>3.8747989116402817</v>
       </c>
       <c r="J36" s="0">
-        <v>2.8340080971659893</v>
+        <v>2.3555391976444589</v>
       </c>
       <c r="K36" s="0">
-        <v>1.9329896907216479</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L36" s="0">
-        <v>3.8223493919696416</v>
+        <v>3.7026093988119273</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>3.5025105838338062</v>
+        <v>3.0890026582652332</v>
       </c>
       <c r="B37" s="0">
-        <v>1.3157894736842093</v>
+        <v>0.78947368421052566</v>
       </c>
       <c r="C37" s="0">
-        <v>4.2100457779074008</v>
+        <v>3.2767344247327479</v>
       </c>
       <c r="D37" s="0">
-        <v>4.3036087803236089</v>
+        <v>3.1976534513018988</v>
       </c>
       <c r="E37" s="0">
-        <v>3.4654971807034785</v>
+        <v>3.3742056743936244</v>
       </c>
       <c r="F37" s="0">
-        <v>3.6222392024160355</v>
+        <v>3.3238729396354083</v>
       </c>
       <c r="G37" s="0">
-        <v>2.4341178837256066</v>
+        <v>3.4399517199758574</v>
       </c>
       <c r="H37" s="0">
-        <v>2.613190933363629</v>
+        <v>2.4995739362608624</v>
       </c>
       <c r="I37" s="0">
-        <v>3.9323945899783483</v>
+        <v>3.7496772655955164</v>
       </c>
       <c r="J37" s="0">
-        <v>2.6683842473316131</v>
+        <v>2.5211630474788347</v>
       </c>
       <c r="K37" s="0">
-        <v>0.38659793814432958</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L37" s="0">
-        <v>3.606195378347274</v>
+        <v>3.5719839517307843</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>3.3769813921433465</v>
+        <v>2.9462439696760829</v>
       </c>
       <c r="B38" s="0">
-        <v>0.61403508771929771</v>
+        <v>0.96491228070175361</v>
       </c>
       <c r="C38" s="0">
-        <v>4.0160286080219088</v>
+        <v>3.0484789307498166</v>
       </c>
       <c r="D38" s="0">
-        <v>3.5102060442862948</v>
+        <v>3.3250787392109222</v>
       </c>
       <c r="E38" s="0">
-        <v>3.2608371371460936</v>
+        <v>3.2298099585309799</v>
       </c>
       <c r="F38" s="0">
-        <v>3.3602590692428018</v>
+        <v>2.9236255139540783</v>
       </c>
       <c r="G38" s="0">
-        <v>2.6352846509756565</v>
+        <v>2.9973848320257468</v>
       </c>
       <c r="H38" s="0">
-        <v>2.3745952394478196</v>
+        <v>2.8745100266999914</v>
       </c>
       <c r="I38" s="0">
-        <v>3.4696431054000882</v>
+        <v>3.5093642628746169</v>
       </c>
       <c r="J38" s="0">
-        <v>2.2451232977548745</v>
+        <v>2.3739418476260559</v>
       </c>
       <c r="K38" s="0">
-        <v>0.38659793814432958</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L38" s="0">
-        <v>3.606195378347274</v>
+        <v>3.2749665661058036</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>3.1628433592596212</v>
+        <v>2.8404056315841264</v>
       </c>
       <c r="B39" s="0">
-        <v>0.87719298245613953</v>
+        <v>0.61403508771929771</v>
       </c>
       <c r="C39" s="0">
-        <v>3.6850581417466586</v>
+        <v>2.8595341051750567</v>
       </c>
       <c r="D39" s="0">
-        <v>3.0197388983723195</v>
+        <v>3.4573125285504744</v>
       </c>
       <c r="E39" s="0">
-        <v>3.1045078910468664</v>
+        <v>3.033503386139202</v>
       </c>
       <c r="F39" s="0">
-        <v>3.0473383546192165</v>
+        <v>2.9745660954044295</v>
       </c>
       <c r="G39" s="0">
-        <v>3.1382015691007821</v>
+        <v>2.3536511768255863</v>
       </c>
       <c r="H39" s="0">
-        <v>2.6813611316252888</v>
+        <v>3.2267227177185678</v>
       </c>
       <c r="I39" s="0">
-        <v>3.3643820380925868</v>
+        <v>3.2531627971639066</v>
       </c>
       <c r="J39" s="0">
-        <v>2.0979020979020961</v>
+        <v>2.8340080971659893</v>
       </c>
       <c r="K39" s="0">
-        <v>0.25773195876288635</v>
+        <v>0</v>
       </c>
       <c r="L39" s="0">
-        <v>3.3604951326470287</v>
+        <v>3.1692221565639258</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>3.1751501427586857</v>
+        <v>2.7296445800925446</v>
       </c>
       <c r="B40" s="0">
-        <v>1.1403508771929816</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C40" s="0">
-        <v>3.5037218326379964</v>
+        <v>2.8481213304759101</v>
       </c>
       <c r="D40" s="0">
-        <v>2.9764623854975572</v>
+        <v>3.4621210299810032</v>
       </c>
       <c r="E40" s="0">
-        <v>3.1080879501178411</v>
+        <v>3.0251499149735945</v>
       </c>
       <c r="F40" s="0">
-        <v>2.8490339482589211</v>
+        <v>2.91089036859149</v>
       </c>
       <c r="G40" s="0">
-        <v>3.0577348622007618</v>
+        <v>2.3938845302755962</v>
       </c>
       <c r="H40" s="0">
-        <v>2.9654036243822048</v>
+        <v>3.0676589217746946</v>
       </c>
       <c r="I40" s="0">
-        <v>3.2452185656690009</v>
+        <v>3.0108637365692812</v>
       </c>
       <c r="J40" s="0">
-        <v>2.6315789473684186</v>
+        <v>2.649981597350016</v>
       </c>
       <c r="K40" s="0">
         <v>0</v>
       </c>
       <c r="L40" s="0">
-        <v>3.1972133237955993</v>
+        <v>2.8426585388610679</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>3.2243772767549621</v>
+        <v>2.7616422171901278</v>
       </c>
       <c r="B41" s="0">
         <v>0.35087719298245779</v>
       </c>
       <c r="C41" s="0">
-        <v>3.2678578221889851</v>
+        <v>2.7403340138728747</v>
       </c>
       <c r="D41" s="0">
-        <v>2.8610583511648726</v>
+        <v>3.0870579183997449</v>
       </c>
       <c r="E41" s="0">
-        <v>2.9487753214594847</v>
+        <v>2.8759807870163323</v>
       </c>
       <c r="F41" s="0">
-        <v>2.8435760288178278</v>
+        <v>2.6088854928501379</v>
       </c>
       <c r="G41" s="0">
-        <v>3.3393683363508506</v>
+        <v>2.273184469925579</v>
       </c>
       <c r="H41" s="0">
-        <v>3.0790206214849887</v>
+        <v>2.9313185252513914</v>
       </c>
       <c r="I41" s="0">
-        <v>3.0684594149073647</v>
+        <v>2.9492959424837779</v>
       </c>
       <c r="J41" s="0">
-        <v>3.0180345969819795</v>
+        <v>2.741994847258018</v>
       </c>
       <c r="K41" s="0">
         <v>0</v>
       </c>
       <c r="L41" s="0">
-        <v>2.900195938170635</v>
+        <v>2.8286629552452469</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>2.9265531160775793</v>
+        <v>2.6164221719011494</v>
       </c>
       <c r="B42" s="0">
-        <v>0.52631578947368374</v>
+        <v>0.43859649122806976</v>
       </c>
       <c r="C42" s="0">
-        <v>2.9825384547103031</v>
+        <v>2.5323678971328554</v>
       </c>
       <c r="D42" s="0">
-        <v>3.1303344312744903</v>
+        <v>2.6951650518116006</v>
       </c>
       <c r="E42" s="0">
-        <v>2.8962677884185064</v>
+        <v>2.7059279811450199</v>
       </c>
       <c r="F42" s="0">
-        <v>2.7799003020048731</v>
+        <v>2.4833533457046153</v>
       </c>
       <c r="G42" s="0">
-        <v>3.2589016294508117</v>
+        <v>1.5288674311003809</v>
       </c>
       <c r="H42" s="0">
-        <v>2.7779355791626403</v>
+        <v>2.5847866840879372</v>
       </c>
       <c r="I42" s="0">
-        <v>2.9214911322515911</v>
+        <v>2.6772060137832394</v>
       </c>
       <c r="J42" s="0">
-        <v>2.8340080971659893</v>
+        <v>2.5027603974972377</v>
       </c>
       <c r="K42" s="0">
         <v>0</v>
       </c>
       <c r="L42" s="0">
-        <v>2.7757907504742922</v>
+        <v>2.8193325661680064</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>2.7148764398936671</v>
+        <v>2.6459584522989048</v>
       </c>
       <c r="B43" s="0">
-        <v>0.61403508771929771</v>
+        <v>1.4912280701754372</v>
       </c>
       <c r="C43" s="0">
-        <v>2.9495682166905461</v>
+        <v>2.4791082818701713</v>
       </c>
       <c r="D43" s="0">
-        <v>3.2265044598850738</v>
+        <v>2.2792296780708274</v>
       </c>
       <c r="E43" s="0">
-        <v>2.727408335570868</v>
+        <v>2.6975745099794124</v>
       </c>
       <c r="F43" s="0">
-        <v>2.5979696539679051</v>
+        <v>2.4360513772150036</v>
       </c>
       <c r="G43" s="0">
-        <v>2.5950512975256466</v>
+        <v>1.991550995775496</v>
       </c>
       <c r="H43" s="0">
-        <v>2.8347440777140234</v>
+        <v>2.0905527466909031</v>
       </c>
       <c r="I43" s="0">
-        <v>2.7506901551111174</v>
+        <v>2.5500983098647469</v>
       </c>
       <c r="J43" s="0">
-        <v>2.8524107471475868</v>
+        <v>2.5027603974972377</v>
       </c>
       <c r="K43" s="0">
         <v>0</v>
       </c>
       <c r="L43" s="0">
-        <v>2.6327247846235164</v>
+        <v>2.5238702453892308</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0">
-        <v>2.6607265924977828</v>
+        <v>2.3924387122181723</v>
       </c>
       <c r="B44" s="0">
-        <v>1.1403508771929816</v>
+        <v>1.5789473684210513</v>
       </c>
       <c r="C44" s="0">
-        <v>2.8062744899123726</v>
+        <v>2.2292953245666296</v>
       </c>
       <c r="D44" s="0">
-        <v>3.5727165628831745</v>
+        <v>1.9185920707811392</v>
       </c>
       <c r="E44" s="0">
-        <v>2.6599838897341783</v>
+        <v>2.6468570064739376</v>
       </c>
       <c r="F44" s="0">
-        <v>2.5415711530764447</v>
+        <v>2.1431430338754849</v>
       </c>
       <c r="G44" s="0">
-        <v>2.2530677932005609</v>
+        <v>1.6093341380004007</v>
       </c>
       <c r="H44" s="0">
-        <v>2.4427654377094794</v>
+        <v>2.0280633982843814</v>
       </c>
       <c r="I44" s="0">
-        <v>2.5918055252130023</v>
+        <v>2.480586284284322</v>
       </c>
       <c r="J44" s="0">
-        <v>2.7972027972027949</v>
+        <v>2.0979020979020961</v>
       </c>
       <c r="K44" s="0">
         <v>0</v>
       </c>
       <c r="L44" s="0">
-        <v>2.5254253102354345</v>
+        <v>2.4290112897707812</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0">
-        <v>2.6410357388992791</v>
+        <v>2.1906074628335119</v>
       </c>
       <c r="B45" s="0">
-        <v>0.78947368421052566</v>
+        <v>1.1403508771929816</v>
       </c>
       <c r="C45" s="0">
-        <v>2.6274743529590765</v>
+        <v>2.2001293447799219</v>
       </c>
       <c r="D45" s="0">
-        <v>3.3779722549467426</v>
+        <v>1.694996754261533</v>
       </c>
       <c r="E45" s="0">
-        <v>2.6050896506459003</v>
+        <v>2.49112443688654</v>
       </c>
       <c r="F45" s="0">
-        <v>2.2541207291780356</v>
+        <v>2.1904450023650965</v>
       </c>
       <c r="G45" s="0">
-        <v>2.152484409575536</v>
+        <v>1.7903842285254461</v>
       </c>
       <c r="H45" s="0">
-        <v>2.2837016417656062</v>
+        <v>1.9996591490086899</v>
       </c>
       <c r="I45" s="0">
-        <v>2.2839665547854042</v>
+        <v>2.3058131913963953</v>
       </c>
       <c r="J45" s="0">
-        <v>2.5763709974236271</v>
+        <v>1.6930437983069548</v>
       </c>
       <c r="K45" s="0">
         <v>0</v>
       </c>
       <c r="L45" s="0">
-        <v>2.3839144092308628</v>
+        <v>2.3294871396137196</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0">
-        <v>2.6385743821994661</v>
+        <v>2.3801319287191078</v>
       </c>
       <c r="B46" s="0">
-        <v>1.7543859649122791</v>
+        <v>1.9298245614035072</v>
       </c>
       <c r="C46" s="0">
-        <v>2.4905210565693174</v>
+        <v>1.9858227976515028</v>
       </c>
       <c r="D46" s="0">
-        <v>3.0942706705455216</v>
+        <v>1.6445074892409768</v>
       </c>
       <c r="E46" s="0">
-        <v>2.4958978489811727</v>
+        <v>2.4475670515230146</v>
       </c>
       <c r="F46" s="0">
-        <v>2.1504202597969635</v>
+        <v>2.0740093876214369</v>
       </c>
       <c r="G46" s="0">
-        <v>1.8708509354254659</v>
+        <v>2.5145845906256263</v>
       </c>
       <c r="H46" s="0">
-        <v>2.0280633982843814</v>
+        <v>1.8405953530648167</v>
       </c>
       <c r="I46" s="0">
-        <v>2.272050207543046</v>
+        <v>2.0933049989076662</v>
       </c>
       <c r="J46" s="0">
-        <v>2.1715126978284855</v>
+        <v>1.5642252484357733</v>
       </c>
       <c r="K46" s="0">
         <v>0.12886597938144317</v>
       </c>
       <c r="L46" s="0">
-        <v>2.3730289553074342</v>
+        <v>2.2641744160731481</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0">
-        <v>2.3973614256178117</v>
+        <v>2.1438416855370779</v>
       </c>
       <c r="B47" s="0">
-        <v>2.6315789473684332</v>
+        <v>3.2456140350877343</v>
       </c>
       <c r="C47" s="0">
-        <v>2.467695507171038</v>
+        <v>1.8095588328535823</v>
       </c>
       <c r="D47" s="0">
-        <v>2.6254417810689423</v>
+        <v>1.7334647657057758</v>
       </c>
       <c r="E47" s="0">
-        <v>2.4159431963960851</v>
+        <v>2.3300217786926925</v>
       </c>
       <c r="F47" s="0">
-        <v>2.2577593421387872</v>
+        <v>2.0303460320925759</v>
       </c>
       <c r="G47" s="0">
-        <v>1.6696841681754253</v>
+        <v>2.0317843492255174</v>
       </c>
       <c r="H47" s="0">
-        <v>1.9314889507470407</v>
+        <v>2.028063398284393</v>
       </c>
       <c r="I47" s="0">
-        <v>2.1072074040237632</v>
+        <v>2.0357093205696111</v>
       </c>
       <c r="J47" s="0">
-        <v>1.9690835480309257</v>
+        <v>1.4722119985277948</v>
       </c>
       <c r="K47" s="0">
-        <v>0</v>
+        <v>0.1288659793814439</v>
       </c>
       <c r="L47" s="0">
-        <v>2.1102229962989556</v>
+        <v>2.1319939041458129</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>2.3555183617209785</v>
+        <v>2.0453874175445486</v>
       </c>
       <c r="B48" s="0">
-        <v>2.9824561403508745</v>
+        <v>2.4561403508771908</v>
       </c>
       <c r="C48" s="0">
-        <v>2.2508527878872395</v>
+        <v>1.8222396936304019</v>
       </c>
       <c r="D48" s="0">
-        <v>2.2191234101892126</v>
+        <v>1.8128050393094974</v>
       </c>
       <c r="E48" s="0">
-        <v>2.2518571556430662</v>
+        <v>2.2452937140129459</v>
       </c>
       <c r="F48" s="0">
-        <v>2.0503584033766309</v>
+        <v>1.9175490303096443</v>
       </c>
       <c r="G48" s="0">
-        <v>1.7300341983504308</v>
+        <v>1.8708509354254659</v>
       </c>
       <c r="H48" s="0">
-        <v>1.9485315003124453</v>
+        <v>2.0223825484292433</v>
       </c>
       <c r="I48" s="0">
-        <v>1.9364064268832777</v>
+        <v>1.7934102599749742</v>
       </c>
       <c r="J48" s="0">
-        <v>1.7666543982333442</v>
+        <v>1.8954729481045254</v>
       </c>
       <c r="K48" s="0">
-        <v>0.12886597938144317</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L48" s="0">
-        <v>2.0309146891425351</v>
+        <v>1.9049544366000044</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>2.2324505267303318</v>
+        <v>1.9690853598503477</v>
       </c>
       <c r="B49" s="0">
-        <v>2.8947368421052606</v>
+        <v>4.0350877192982422</v>
       </c>
       <c r="C49" s="0">
-        <v>2.1595505902940673</v>
+        <v>1.7296694099595464</v>
       </c>
       <c r="D49" s="0">
-        <v>1.8656985550453185</v>
+        <v>1.6541244921020351</v>
       </c>
       <c r="E49" s="0">
-        <v>2.2106864763268574</v>
+        <v>2.1683224439869906</v>
       </c>
       <c r="F49" s="0">
-        <v>1.9721282247207348</v>
+        <v>1.8593312229378143</v>
       </c>
       <c r="G49" s="0">
-        <v>2.2128344397505515</v>
+        <v>1.5288674311003809</v>
       </c>
       <c r="H49" s="0">
-        <v>1.9485315003124453</v>
+        <v>2.0223825484292433</v>
       </c>
       <c r="I49" s="0">
-        <v>1.7596472761216246</v>
+        <v>1.6444559194454911</v>
       </c>
       <c r="J49" s="0">
-        <v>1.6378358483621627</v>
+        <v>2.0426941479573042</v>
       </c>
       <c r="K49" s="0">
-        <v>0</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L49" s="0">
-        <v>1.9391658632164945</v>
+        <v>1.8443069075980452</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0">
-        <v>2.0773850546421166</v>
+        <v>2.0158511371467935</v>
       </c>
       <c r="B50" s="0">
-        <v>2.5438596491228047</v>
+        <v>2.9824561403508745</v>
       </c>
       <c r="C50" s="0">
-        <v>1.9731419368746734</v>
+        <v>1.6256863515895443</v>
       </c>
       <c r="D50" s="0">
-        <v>1.7286562642752372</v>
+        <v>1.5363162070540701</v>
       </c>
       <c r="E50" s="0">
-        <v>2.1295384707180984</v>
+        <v>2.0973179390793262</v>
       </c>
       <c r="F50" s="0">
-        <v>1.9412000145544501</v>
+        <v>1.6701233489793677</v>
       </c>
       <c r="G50" s="0">
-        <v>2.2530677932005609</v>
+        <v>1.4886340776503708</v>
       </c>
       <c r="H50" s="0">
-        <v>1.9882974492984133</v>
+        <v>2.0167016985741051</v>
       </c>
       <c r="I50" s="0">
-        <v>1.6504140930666706</v>
+        <v>1.6484280351929441</v>
       </c>
       <c r="J50" s="0">
-        <v>1.545822598454176</v>
+        <v>1.8402649981597332</v>
       </c>
       <c r="K50" s="0">
-        <v>0.25773195876288635</v>
+        <v>0.64432989690721587</v>
       </c>
       <c r="L50" s="0">
-        <v>1.9282804092930657</v>
+        <v>1.8209809349049839</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>2.0970759082406203</v>
+        <v>1.7795608939647518</v>
       </c>
       <c r="B51" s="0">
-        <v>3.4210526315789447</v>
+        <v>2.8070175438596467</v>
       </c>
       <c r="C51" s="0">
-        <v>1.9312950963111362</v>
+        <v>1.5749629084822265</v>
       </c>
       <c r="D51" s="0">
-        <v>1.7502945207126186</v>
+        <v>1.4714014377419264</v>
       </c>
       <c r="E51" s="0">
-        <v>2.0501804946448265</v>
+        <v>2.0537605537158013</v>
       </c>
       <c r="F51" s="0">
-        <v>1.8757049812611415</v>
+        <v>1.6937743332241735</v>
       </c>
       <c r="G51" s="0">
-        <v>2.4140012070006014</v>
+        <v>1.4081673707503508</v>
       </c>
       <c r="H51" s="0">
-        <v>2.1416803953871484</v>
+        <v>1.8974038516162002</v>
       </c>
       <c r="I51" s="0">
-        <v>1.5987765883497831</v>
+        <v>1.4657107108101117</v>
       </c>
       <c r="J51" s="0">
-        <v>1.601030548398968</v>
+        <v>1.821862348178136</v>
       </c>
       <c r="K51" s="0">
-        <v>0.5154639175257727</v>
+        <v>1.1597938144329887</v>
       </c>
       <c r="L51" s="0">
-        <v>1.8116505458277596</v>
+        <v>1.5986066618977997</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0">
-        <v>2.101998621640246</v>
+        <v>1.7254110465688672</v>
       </c>
       <c r="B52" s="0">
-        <v>2.9824561403508745</v>
+        <v>1.6666666666666652</v>
       </c>
       <c r="C52" s="0">
-        <v>1.8564780177278417</v>
+        <v>1.5381884122294207</v>
       </c>
       <c r="D52" s="0">
-        <v>1.6060394777967433</v>
+        <v>1.1997211069170284</v>
       </c>
       <c r="E52" s="0">
-        <v>1.8914645424982828</v>
+        <v>1.9624690474059472</v>
       </c>
       <c r="F52" s="0">
-        <v>1.6537495906560404</v>
+        <v>1.582796637921623</v>
       </c>
       <c r="G52" s="0">
-        <v>1.7702675518004409</v>
+        <v>1.4081673707503508</v>
       </c>
       <c r="H52" s="0">
-        <v>1.8917230017610618</v>
+        <v>1.6701698574106672</v>
       </c>
       <c r="I52" s="0">
-        <v>1.4637246529363852</v>
+        <v>1.42201743758813</v>
       </c>
       <c r="J52" s="0">
-        <v>1.821862348178136</v>
+        <v>1.601030548398968</v>
       </c>
       <c r="K52" s="0">
-        <v>0.5154639175257727</v>
+        <v>0.90206185567010222</v>
       </c>
       <c r="L52" s="0">
-        <v>1.6981308120548613</v>
+        <v>1.7074612011320855</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0">
-        <v>1.9321650093531537</v>
+        <v>1.4275868858915022</v>
       </c>
       <c r="B53" s="0">
-        <v>2.1052631578947349</v>
+        <v>1.5789473684210513</v>
       </c>
       <c r="C53" s="0">
-        <v>1.7639077340569862</v>
+        <v>1.4025032019173449</v>
       </c>
       <c r="D53" s="0">
-        <v>1.7887625321568517</v>
+        <v>1.0939340754453866</v>
       </c>
       <c r="E53" s="0">
-        <v>1.8502938631820742</v>
+        <v>1.8789343357498716</v>
       </c>
       <c r="F53" s="0">
-        <v>1.6537495906560404</v>
+        <v>1.5864352508823623</v>
       </c>
       <c r="G53" s="0">
-        <v>1.569100784550391</v>
+        <v>1.1466505733252856</v>
       </c>
       <c r="H53" s="0">
-        <v>1.7610634550928805</v>
+        <v>1.5395103107424857</v>
       </c>
       <c r="I53" s="0">
-        <v>1.3783241643661484</v>
+        <v>1.2750491549323735</v>
       </c>
       <c r="J53" s="0">
-        <v>1.5642252484357733</v>
+        <v>1.4722119985277868</v>
       </c>
       <c r="K53" s="0">
-        <v>0.5154639175257727</v>
+        <v>0.64432989690721587</v>
       </c>
       <c r="L53" s="0">
-        <v>1.6359282182066979</v>
+        <v>1.5099679656641669</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0">
-        <v>1.8189426011617589</v>
+        <v>1.4866594466870125</v>
       </c>
       <c r="B54" s="0">
-        <v>1.2280701754385954</v>
+        <v>1.8421052631578929</v>
       </c>
       <c r="C54" s="0">
-        <v>1.6130054908127152</v>
+        <v>1.3365627258778314</v>
       </c>
       <c r="D54" s="0">
-        <v>1.8128050393094974</v>
+        <v>0.92563652537686547</v>
       </c>
       <c r="E54" s="0">
-        <v>1.8747576001670676</v>
+        <v>1.7661624750141693</v>
       </c>
       <c r="F54" s="0">
-        <v>1.6755812684204767</v>
+        <v>1.4408907324527875</v>
       </c>
       <c r="G54" s="0">
-        <v>1.4685174009253659</v>
+        <v>1.4282840474753558</v>
       </c>
       <c r="H54" s="0">
-        <v>1.6928932568312205</v>
+        <v>1.352042265522921</v>
       </c>
       <c r="I54" s="0">
-        <v>1.4458501320728472</v>
+        <v>1.2234116502154861</v>
       </c>
       <c r="J54" s="0">
-        <v>1.8770702981229279</v>
+        <v>1.3986013986013974</v>
       </c>
       <c r="K54" s="0">
-        <v>1.0309278350515454</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L54" s="0">
-        <v>1.5192983547413914</v>
+        <v>1.4057786209684931</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0">
-        <v>1.7155656197696154</v>
+        <v>1.356207541596927</v>
       </c>
       <c r="B55" s="0">
-        <v>1.6666666666666652</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C55" s="0">
-        <v>1.5217032932195425</v>
+        <v>1.3352946398001484</v>
       </c>
       <c r="D55" s="0">
-        <v>1.6493159906715056</v>
+        <v>0.79580698675257788</v>
       </c>
       <c r="E55" s="0">
-        <v>1.7464721501238087</v>
+        <v>1.6301202303171321</v>
       </c>
       <c r="F55" s="0">
-        <v>1.4991085398246176</v>
+        <v>1.4936506203835085</v>
       </c>
       <c r="G55" s="0">
-        <v>1.1265338966002805</v>
+        <v>1.1667672500502908</v>
       </c>
       <c r="H55" s="0">
-        <v>1.4770209623359642</v>
+        <v>1.1418508208828031</v>
       </c>
       <c r="I55" s="0">
-        <v>1.1757462612460516</v>
+        <v>1.167802029751146</v>
       </c>
       <c r="J55" s="0">
-        <v>1.6194331983805654</v>
+        <v>1.0489510489510481</v>
       </c>
       <c r="K55" s="0">
-        <v>0.77319587628865916</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L55" s="0">
-        <v>1.4415451124311871</v>
+        <v>1.4057786209684931</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0">
-        <v>1.5875750713793428</v>
+        <v>1.393127892094121</v>
       </c>
       <c r="B56" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.35087719298245584</v>
       </c>
       <c r="C56" s="0">
-        <v>1.4481543007139313</v>
+        <v>1.188196654788926</v>
       </c>
       <c r="D56" s="0">
-        <v>1.4425504291587514</v>
+        <v>0.70444545957252358</v>
       </c>
       <c r="E56" s="0">
-        <v>1.5859661684417781</v>
+        <v>1.5835794623944615</v>
       </c>
       <c r="F56" s="0">
-        <v>1.4499872648546361</v>
+        <v>1.2407670196121228</v>
       </c>
       <c r="G56" s="0">
-        <v>1.2874673104003207</v>
+        <v>1.2271172802253056</v>
       </c>
       <c r="H56" s="0">
-        <v>1.5224677611770707</v>
+        <v>1.1986593194341861</v>
       </c>
       <c r="I56" s="0">
-        <v>1.1618438561299667</v>
+        <v>1.0585688466961918</v>
       </c>
       <c r="J56" s="0">
-        <v>1.5090172984909813</v>
+        <v>1.2145748987854241</v>
       </c>
       <c r="K56" s="0">
-        <v>0.5154639175257727</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L56" s="0">
-        <v>1.3669019998133909</v>
+        <v>1.3093646005038397</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0">
-        <v>1.491582160086655</v>
+        <v>1.2872895540021792</v>
       </c>
       <c r="B57" s="0">
-        <v>0.52631578947368962</v>
+        <v>0.35087719298245973</v>
       </c>
       <c r="C57" s="0">
-        <v>1.492537313432851</v>
+        <v>1.1171838344386931</v>
       </c>
       <c r="D57" s="0">
-        <v>1.2598273747986568</v>
+        <v>0.7092539610030606</v>
       </c>
       <c r="E57" s="0">
-        <v>1.533458635400833</v>
+        <v>1.5310719293535167</v>
       </c>
       <c r="F57" s="0">
-        <v>1.3317323436306217</v>
+        <v>1.2807917621802698</v>
       </c>
       <c r="G57" s="0">
-        <v>1.207000603500314</v>
+        <v>1.2874673104003351</v>
       </c>
       <c r="H57" s="0">
-        <v>1.2270635687098914</v>
+        <v>1.2725103675509986</v>
       </c>
       <c r="I57" s="0">
-        <v>1.1896486663621499</v>
+        <v>1.0943178884232798</v>
       </c>
       <c r="J57" s="0">
-        <v>1.2697828487302303</v>
+        <v>0.92013249907987682</v>
       </c>
       <c r="K57" s="0">
-        <v>0.25773195876288924</v>
+        <v>0.38659793814433385</v>
       </c>
       <c r="L57" s="0">
-        <v>1.2642677199639354</v>
+        <v>1.2518272011943026</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0">
-        <v>1.5728069311804653</v>
+        <v>1.1666830757113311</v>
       </c>
       <c r="B58" s="0">
-        <v>0.43859649122806976</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C58" s="0">
-        <v>1.2845711966928304</v>
+        <v>0.98149862412660482</v>
       </c>
       <c r="D58" s="0">
-        <v>0.9424662803837176</v>
+        <v>0.69242420599620058</v>
       </c>
       <c r="E58" s="0">
-        <v>1.4791610728243669</v>
+        <v>1.3729526537187853</v>
       </c>
       <c r="F58" s="0">
-        <v>1.2716952297784072</v>
+        <v>1.1916457446421413</v>
       </c>
       <c r="G58" s="0">
-        <v>1.3478173405753358</v>
+        <v>1.1868839267752955</v>
       </c>
       <c r="H58" s="0">
-        <v>1.2497869681304312</v>
+        <v>1.3293188661023678</v>
       </c>
       <c r="I58" s="0">
-        <v>1.0565827888224653</v>
+        <v>0.90167027467180316</v>
       </c>
       <c r="J58" s="0">
-        <v>1.4170040485829947</v>
+        <v>0.88332719911667212</v>
       </c>
       <c r="K58" s="0">
-        <v>0.64432989690721587</v>
+        <v>0</v>
       </c>
       <c r="L58" s="0">
         <v>1.2891487575031866</v>
@@ -2276,1235 +2277,1235 @@
     </row>
     <row r="59">
       <c r="A59" s="0">
-        <v>1.3586688982967401</v>
+        <v>1.1297627252141369</v>
       </c>
       <c r="B59" s="0">
-        <v>0.087719298245613961</v>
+        <v>0</v>
       </c>
       <c r="C59" s="0">
-        <v>1.1856604826335599</v>
+        <v>0.98783905451501963</v>
       </c>
       <c r="D59" s="0">
-        <v>0.8775515110715737</v>
+        <v>0.59144567595508812</v>
       </c>
       <c r="E59" s="0">
-        <v>1.3466988871983043</v>
+        <v>1.2518273218174756</v>
       </c>
       <c r="F59" s="0">
-        <v>1.2262125677691653</v>
+        <v>1.1861878252010323</v>
       </c>
       <c r="G59" s="0">
-        <v>1.0460671897002607</v>
+        <v>0.76443371555019046</v>
       </c>
       <c r="H59" s="0">
-        <v>1.1588933704482181</v>
+        <v>1.2781912174061227</v>
       </c>
       <c r="I59" s="0">
-        <v>0.88776786955571807</v>
+        <v>0.87386546443963287</v>
       </c>
       <c r="J59" s="0">
-        <v>0.99374309900625601</v>
+        <v>1.1777695988222294</v>
       </c>
       <c r="K59" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L59" s="0">
-        <v>1.2409417472708602</v>
+        <v>1.094765651727676</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0">
-        <v>1.1568376489120793</v>
+        <v>0.97469725312592215</v>
       </c>
       <c r="B60" s="0">
         <v>0.26315789473684187</v>
       </c>
       <c r="C60" s="0">
-        <v>1.1273285230601444</v>
+        <v>0.85976236066904144</v>
       </c>
       <c r="D60" s="0">
-        <v>0.76214747673887362</v>
+        <v>0.62991368739932141</v>
       </c>
       <c r="E60" s="0">
-        <v>1.2613741460067414</v>
+        <v>1.2076732599421214</v>
       </c>
       <c r="F60" s="0">
-        <v>1.1661754539169658</v>
+        <v>1.1370665502310511</v>
       </c>
       <c r="G60" s="0">
-        <v>1.1868839267752955</v>
+        <v>0.82478374572520541</v>
       </c>
       <c r="H60" s="0">
-        <v>1.3236380162472294</v>
+        <v>1.1077657217519732</v>
       </c>
       <c r="I60" s="0">
-        <v>0.84804671208118931</v>
+        <v>0.87187940656590657</v>
       </c>
       <c r="J60" s="0">
-        <v>0.93853514906146396</v>
+        <v>1.0857563489142428</v>
       </c>
       <c r="K60" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L60" s="0">
-        <v>1.1227568189593495</v>
+        <v>1.0434485118029413</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0">
-        <v>1.2774441272029131</v>
+        <v>0.95746775622723157</v>
       </c>
       <c r="B61" s="0">
         <v>0.087719298245613961</v>
       </c>
       <c r="C61" s="0">
-        <v>1.1070391458172171</v>
+        <v>0.90541345946562768</v>
       </c>
       <c r="D61" s="0">
-        <v>0.74531772173202149</v>
+        <v>0.55778616594138386</v>
       </c>
       <c r="E61" s="0">
-        <v>1.173662698767862</v>
+        <v>1.1038515468838559</v>
       </c>
       <c r="F61" s="0">
-        <v>1.1134155659862452</v>
+        <v>0.9897027253211067</v>
       </c>
       <c r="G61" s="0">
-        <v>1.1868839267752955</v>
+        <v>0.68396700865017046</v>
       </c>
       <c r="H61" s="0">
-        <v>1.1532125205930797</v>
+        <v>1.0907231721865582</v>
       </c>
       <c r="I61" s="0">
-        <v>0.82818613334392499</v>
+        <v>0.80236738098548122</v>
       </c>
       <c r="J61" s="0">
-        <v>0.77291129922708801</v>
+        <v>1.0305483989694506</v>
       </c>
       <c r="K61" s="0">
         <v>0</v>
       </c>
       <c r="L61" s="0">
-        <v>1.0823251329580434</v>
+        <v>1.0139022797250636</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>1.0190016737225549</v>
+        <v>0.79994092743920375</v>
       </c>
       <c r="B62" s="0">
-        <v>0.43859649122806976</v>
+        <v>0.52631578947368374</v>
       </c>
       <c r="C62" s="0">
-        <v>1.0766050799528264</v>
+        <v>0.76972824915355187</v>
       </c>
       <c r="D62" s="0">
-        <v>0.69963695814199434</v>
+        <v>0.50248839949029833</v>
       </c>
       <c r="E62" s="0">
-        <v>1.1044482233956852</v>
+        <v>1.0465706017482612</v>
       </c>
       <c r="F62" s="0">
-        <v>0.93694283739038586</v>
+        <v>0.87508641705781676</v>
       </c>
       <c r="G62" s="0">
-        <v>1.3075839871253259</v>
+        <v>0.68396700865017046</v>
       </c>
       <c r="H62" s="0">
-        <v>1.1134465716071114</v>
+        <v>0.96006362551837676</v>
       </c>
       <c r="I62" s="0">
-        <v>0.77456257075331114</v>
+        <v>0.74278564477368803</v>
       </c>
       <c r="J62" s="0">
-        <v>0.93853514906146396</v>
+        <v>0.97534044902465866</v>
       </c>
       <c r="K62" s="0">
         <v>0</v>
       </c>
       <c r="L62" s="0">
-        <v>1.0061269554940431</v>
+        <v>0.97036046403134924</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>1.0165403170227421</v>
+        <v>0.76548193364182271</v>
       </c>
       <c r="B63" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.52631578947368374</v>
       </c>
       <c r="C63" s="0">
-        <v>0.94852838610684809</v>
+        <v>0.72914949466769741</v>
       </c>
       <c r="D63" s="0">
-        <v>0.71165821171831734</v>
+        <v>0.36063760728968786</v>
       </c>
       <c r="E63" s="0">
-        <v>1.0059965989438817</v>
+        <v>0.99107968614815378</v>
       </c>
       <c r="F63" s="0">
-        <v>1.0497398391733062</v>
+        <v>0.88236364297929548</v>
       </c>
       <c r="G63" s="0">
-        <v>1.0259505129752555</v>
+        <v>0.64373365520016035</v>
       </c>
       <c r="H63" s="0">
-        <v>1.1020848718968348</v>
+        <v>0.92029767653240835</v>
       </c>
       <c r="I63" s="0">
-        <v>0.72491112391015011</v>
+        <v>0.62759428809755458</v>
       </c>
       <c r="J63" s="0">
-        <v>0.97534044902465866</v>
+        <v>0.90172984909826925</v>
       </c>
       <c r="K63" s="0">
         <v>0</v>
       </c>
       <c r="L63" s="0">
-        <v>0.96569526949273687</v>
+        <v>0.89260722172114493</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0">
-        <v>0.94023825932854099</v>
+        <v>0.77532736044107442</v>
       </c>
       <c r="B64" s="0">
-        <v>0.26315789473684187</v>
+        <v>0.96491228070175361</v>
       </c>
       <c r="C64" s="0">
-        <v>0.9003411151548959</v>
+        <v>0.74943887191062464</v>
       </c>
       <c r="D64" s="0">
-        <v>0.63231793811458603</v>
+        <v>0.28370158440122112</v>
       </c>
       <c r="E64" s="0">
-        <v>0.90157820937378719</v>
+        <v>0.83833049911990143</v>
       </c>
       <c r="F64" s="0">
-        <v>1.0206309354873913</v>
+        <v>0.83688098097005348</v>
       </c>
       <c r="G64" s="0">
-        <v>0.94548380607523552</v>
+        <v>0.76443371555019046</v>
       </c>
       <c r="H64" s="0">
-        <v>1.0168721240697598</v>
+        <v>0.77259558029881203</v>
       </c>
       <c r="I64" s="0">
-        <v>0.69909237155170645</v>
+        <v>0.60574765148656373</v>
       </c>
       <c r="J64" s="0">
-        <v>0.92013249907986661</v>
+        <v>0.68089804931910136</v>
       </c>
       <c r="K64" s="0">
         <v>0</v>
       </c>
       <c r="L64" s="0">
-        <v>0.92215345379902258</v>
+        <v>0.86617111933567559</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0">
-        <v>0.87624298513340482</v>
+        <v>0.718716156345377</v>
       </c>
       <c r="B65" s="0">
-        <v>0.52631578947368374</v>
+        <v>0.96491228070175361</v>
       </c>
       <c r="C65" s="0">
-        <v>0.815379347950138</v>
+        <v>0.62136217806464644</v>
       </c>
       <c r="D65" s="0">
-        <v>0.60827543096194026</v>
+        <v>0.29091433654701487</v>
       </c>
       <c r="E65" s="0">
-        <v>0.83833049911990143</v>
+        <v>0.76732599421223713</v>
       </c>
       <c r="F65" s="0">
-        <v>0.92602699850816783</v>
+        <v>0.77502456063748426</v>
       </c>
       <c r="G65" s="0">
-        <v>0.76443371555019046</v>
+        <v>0.70408368537517541</v>
       </c>
       <c r="H65" s="0">
-        <v>0.97710617508379172</v>
+        <v>0.80099982957450366</v>
       </c>
       <c r="I65" s="0">
-        <v>0.63752457746618674</v>
+        <v>0.583901014875573</v>
       </c>
       <c r="J65" s="0">
-        <v>1.0857563489142428</v>
+        <v>0.71770334928229607</v>
       </c>
       <c r="K65" s="0">
         <v>0</v>
       </c>
       <c r="L65" s="0">
-        <v>0.83662488725779793</v>
+        <v>0.77908748794824678</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>0.84670670473564946</v>
+        <v>0.63010731515211127</v>
       </c>
       <c r="B66" s="0">
-        <v>0.87719298245613953</v>
+        <v>1.0526315789473675</v>
       </c>
       <c r="C66" s="0">
-        <v>0.80903891756172341</v>
+        <v>0.56049404633586475</v>
       </c>
       <c r="D66" s="0">
-        <v>0.49287139662924007</v>
+        <v>0.28129733368595655</v>
       </c>
       <c r="E66" s="0">
-        <v>0.78343626003162314</v>
+        <v>0.71004504907664245</v>
       </c>
       <c r="F66" s="0">
-        <v>0.85689335225412</v>
+        <v>0.74773496343193913</v>
       </c>
       <c r="G66" s="0">
-        <v>0.6638503319251654</v>
+        <v>0.70408368537517541</v>
       </c>
       <c r="H66" s="0">
-        <v>0.75555303073339708</v>
+        <v>0.72146793160256717</v>
       </c>
       <c r="I66" s="0">
-        <v>0.59184524637047875</v>
+        <v>0.5541101467696764</v>
       </c>
       <c r="J66" s="0">
-        <v>0.86492454913507477</v>
+        <v>0.93853514906146396</v>
       </c>
       <c r="K66" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L66" s="0">
-        <v>0.78219761764065487</v>
+        <v>0.76042670979379767</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>0.78517278724032613</v>
+        <v>0.59564832135473023</v>
       </c>
       <c r="B67" s="0">
-        <v>1.1403508771929816</v>
+        <v>0.87719298245613953</v>
       </c>
       <c r="C67" s="0">
-        <v>0.76592399092050301</v>
+        <v>0.52752380831610801</v>
       </c>
       <c r="D67" s="0">
-        <v>0.45680763590027129</v>
+        <v>0.30293559012333776</v>
       </c>
       <c r="E67" s="0">
-        <v>0.68796801813896535</v>
+        <v>0.62293027834959225</v>
       </c>
       <c r="F67" s="0">
-        <v>0.79685623840192055</v>
+        <v>0.72772259214787249</v>
       </c>
       <c r="G67" s="0">
-        <v>0.62361697847515529</v>
+        <v>0.52303359485013035</v>
       </c>
       <c r="H67" s="0">
-        <v>0.72714878145770534</v>
+        <v>0.60217008464466237</v>
       </c>
       <c r="I67" s="0">
-        <v>0.51836110504260047</v>
+        <v>0.48459812118925105</v>
       </c>
       <c r="J67" s="0">
-        <v>0.77291129922708801</v>
+        <v>0.68089804931910136</v>
       </c>
       <c r="K67" s="0">
         <v>0</v>
       </c>
       <c r="L67" s="0">
-        <v>0.74954125587036913</v>
+        <v>0.68267346748359348</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>0.67441173574874402</v>
+        <v>0.5341144038594069</v>
       </c>
       <c r="B68" s="0">
-        <v>1.1403508771929816</v>
+        <v>1.2280701754385954</v>
       </c>
       <c r="C68" s="0">
-        <v>0.71900480604623385</v>
+        <v>0.49582165637403425</v>
       </c>
       <c r="D68" s="0">
-        <v>0.28129733368595655</v>
+        <v>0.25965907724857523</v>
       </c>
       <c r="E68" s="0">
-        <v>0.58832304066350383</v>
+        <v>0.57996956949789624</v>
       </c>
       <c r="F68" s="0">
-        <v>0.66950478477604281</v>
+        <v>0.62402212276680069</v>
       </c>
       <c r="G68" s="0">
-        <v>0.64373365520016035</v>
+        <v>0.54315027157513529</v>
       </c>
       <c r="H68" s="0">
-        <v>0.65897858319604552</v>
+        <v>0.66465943305118391</v>
       </c>
       <c r="I68" s="0">
-        <v>0.4230303271037314</v>
+        <v>0.45282119520962805</v>
       </c>
       <c r="J68" s="0">
-        <v>0.79131394920868536</v>
+        <v>0.4600662495399333</v>
       </c>
       <c r="K68" s="0">
         <v>0</v>
       </c>
       <c r="L68" s="0">
-        <v>0.71843995894628743</v>
+        <v>0.65001710571330762</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0">
-        <v>0.62764595845230531</v>
+        <v>0.42089199566801655</v>
       </c>
       <c r="B69" s="0">
-        <v>1.5789473684210689</v>
+        <v>1.1403508771929942</v>
       </c>
       <c r="C69" s="0">
-        <v>0.6251664362977023</v>
+        <v>0.41085988916928101</v>
       </c>
       <c r="D69" s="0">
-        <v>0.28370158440122423</v>
+        <v>0.22599956723487358</v>
       </c>
       <c r="E69" s="0">
-        <v>0.49941824040097166</v>
+        <v>0.48450132760524373</v>
       </c>
       <c r="F69" s="0">
-        <v>0.71680675326566246</v>
+        <v>0.60037113852200152</v>
       </c>
       <c r="G69" s="0">
-        <v>0.72420036210018846</v>
+        <v>0.36210018105009423</v>
       </c>
       <c r="H69" s="0">
-        <v>0.78963812986423576</v>
+        <v>0.80668067942965094</v>
       </c>
       <c r="I69" s="0">
-        <v>0.46076542670453885</v>
+        <v>0.42700244285118899</v>
       </c>
       <c r="J69" s="0">
-        <v>0.64409274935591387</v>
+        <v>0.53367684946632865</v>
       </c>
       <c r="K69" s="0">
         <v>0</v>
       </c>
       <c r="L69" s="0">
-        <v>0.63602152209747798</v>
+        <v>0.62513606817404932</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0">
-        <v>0.56611204095697498</v>
+        <v>0.54642118735847156</v>
       </c>
       <c r="B70" s="0">
         <v>0.96491228070175361</v>
       </c>
       <c r="C70" s="0">
-        <v>0.61375366159854883</v>
+        <v>0.370281134683422</v>
       </c>
       <c r="D70" s="0">
-        <v>0.26206332796383985</v>
+        <v>0.2356165700959294</v>
       </c>
       <c r="E70" s="0">
-        <v>0.47614785643963081</v>
+        <v>0.42901041200513101</v>
       </c>
       <c r="F70" s="0">
-        <v>0.59491321908088579</v>
+        <v>0.51668304042498958</v>
       </c>
       <c r="G70" s="0">
-        <v>0.54315027157513529</v>
+        <v>0.34198350432508523</v>
       </c>
       <c r="H70" s="0">
-        <v>0.64193603363063056</v>
+        <v>0.60217008464466237</v>
       </c>
       <c r="I70" s="0">
-        <v>0.39323945899783486</v>
+        <v>0.38330916962920264</v>
       </c>
       <c r="J70" s="0">
-        <v>0.66249539933750401</v>
+        <v>0.55207949944792001</v>
       </c>
       <c r="K70" s="0">
         <v>0</v>
       </c>
       <c r="L70" s="0">
-        <v>0.66245762448294032</v>
+        <v>0.57692905794171567</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0">
-        <v>0.56611204095697498</v>
+        <v>0.42089199566801189</v>
       </c>
       <c r="B71" s="0">
-        <v>0.96491228070175361</v>
+        <v>0.78947368421052566</v>
       </c>
       <c r="C71" s="0">
-        <v>0.57824725142342615</v>
+        <v>0.30053640041085961</v>
       </c>
       <c r="D71" s="0">
-        <v>0.31736109441492533</v>
+        <v>0.19955280936696063</v>
       </c>
       <c r="E71" s="0">
-        <v>0.41946358781586529</v>
+        <v>0.40514335153196662</v>
       </c>
       <c r="F71" s="0">
-        <v>0.59673252556125556</v>
+        <v>0.49121274969981404</v>
       </c>
       <c r="G71" s="0">
-        <v>0.62361697847515529</v>
+        <v>0.32186682760008018</v>
       </c>
       <c r="H71" s="0">
-        <v>0.67602113276146047</v>
+        <v>0.49991478725217248</v>
       </c>
       <c r="I71" s="0">
-        <v>0.39522551687156127</v>
+        <v>0.32571349129113592</v>
       </c>
       <c r="J71" s="0">
-        <v>0.42326094957673871</v>
+        <v>0.5152741994847253</v>
       </c>
       <c r="K71" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L71" s="0">
-        <v>0.54427269617142993</v>
+        <v>0.54738282586383802</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0">
-        <v>0.53411440385940689</v>
+        <v>0.40858521216894716</v>
       </c>
       <c r="B72" s="0">
-        <v>0.87719298245613953</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C72" s="0">
-        <v>0.45777907404354573</v>
+        <v>0.2510810433812245</v>
       </c>
       <c r="D72" s="0">
-        <v>0.28610583511648568</v>
+        <v>0.19474430793643144</v>
       </c>
       <c r="E72" s="0">
-        <v>0.40514335153196662</v>
+        <v>0.35502252453832123</v>
       </c>
       <c r="F72" s="0">
-        <v>0.52577957282683796</v>
+        <v>0.49121274969981404</v>
       </c>
       <c r="G72" s="0">
-        <v>0.50291691812512529</v>
+        <v>0.26151679742506517</v>
       </c>
       <c r="H72" s="0">
-        <v>0.62489348406521561</v>
+        <v>0.45446798841106584</v>
       </c>
       <c r="I72" s="0">
-        <v>0.32174137554368304</v>
+        <v>0.28996444956406003</v>
       </c>
       <c r="J72" s="0">
-        <v>0.55207949944792001</v>
+        <v>0.62569009937430942</v>
       </c>
       <c r="K72" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L72" s="0">
-        <v>0.52405685317077677</v>
+        <v>0.52872204770938902</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0">
-        <v>0.51934626366052916</v>
+        <v>0.37412621837156607</v>
       </c>
       <c r="B73" s="0">
-        <v>0.35087719298245584</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C73" s="0">
-        <v>0.39057051192634923</v>
+        <v>0.21811080536146774</v>
       </c>
       <c r="D73" s="0">
-        <v>0.29812708869280863</v>
+        <v>0.12982953862428762</v>
       </c>
       <c r="E73" s="0">
-        <v>0.33712222918344792</v>
+        <v>0.30669172708016318</v>
       </c>
       <c r="F73" s="0">
-        <v>0.49121274969981404</v>
+        <v>0.46210384601389903</v>
       </c>
       <c r="G73" s="0">
-        <v>0.52303359485013035</v>
+        <v>0.30175015087507517</v>
       </c>
       <c r="H73" s="0">
-        <v>0.52831903652786416</v>
+        <v>0.46014883826620417</v>
       </c>
       <c r="I73" s="0">
-        <v>0.32174137554368304</v>
+        <v>0.25024329208953128</v>
       </c>
       <c r="J73" s="0">
-        <v>0.53367684946632266</v>
+        <v>0.331247699668752</v>
       </c>
       <c r="K73" s="0">
         <v>0</v>
       </c>
       <c r="L73" s="0">
-        <v>0.47895997263085832</v>
+        <v>0.46029919447640927</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0">
-        <v>0.43566013586688945</v>
+        <v>0.31013094417642978</v>
       </c>
       <c r="B74" s="0">
-        <v>0.52631578947368374</v>
+        <v>0.43859649122806976</v>
       </c>
       <c r="C74" s="0">
-        <v>0.33731089666366526</v>
+        <v>0.17753205087561327</v>
       </c>
       <c r="D74" s="0">
-        <v>0.25725482653331067</v>
+        <v>0.098574279325848016</v>
       </c>
       <c r="E74" s="0">
-        <v>0.28700140218980252</v>
+        <v>0.29535487335541011</v>
       </c>
       <c r="F74" s="0">
-        <v>0.47120037841574752</v>
+        <v>0.41116326456354802</v>
       </c>
       <c r="G74" s="0">
-        <v>0.42245021122510523</v>
+        <v>0.30175015087507517</v>
       </c>
       <c r="H74" s="0">
-        <v>0.43742543884565088</v>
+        <v>0.39765948985968264</v>
       </c>
       <c r="I74" s="0">
-        <v>0.2919505074377865</v>
+        <v>0.24825723421580481</v>
       </c>
       <c r="J74" s="0">
-        <v>0.64409274935590677</v>
+        <v>0.38645564961354401</v>
       </c>
       <c r="K74" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L74" s="0">
-        <v>0.45718906478400106</v>
+        <v>0.39032127639722541</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0">
-        <v>0.35197400807324963</v>
+        <v>0.26828788027960992</v>
       </c>
       <c r="B75" s="0">
-        <v>0.26315789473684187</v>
+        <v>0</v>
       </c>
       <c r="C75" s="0">
-        <v>0.3094130029546403</v>
+        <v>0.14075755462280767</v>
       </c>
       <c r="D75" s="0">
-        <v>0.22359531651960646</v>
+        <v>0.086553025749525073</v>
       </c>
       <c r="E75" s="0">
-        <v>0.24702407589725209</v>
+        <v>0.23688057519615718</v>
       </c>
       <c r="F75" s="0">
-        <v>0.43117563584761448</v>
+        <v>0.36204198959356659</v>
       </c>
       <c r="G75" s="0">
-        <v>0.30175015087507517</v>
+        <v>0.16093341380004009</v>
       </c>
       <c r="H75" s="0">
-        <v>0.34653184116343771</v>
+        <v>0.3351701414531611</v>
       </c>
       <c r="I75" s="0">
-        <v>0.28003416019542787</v>
+        <v>0.23038271335226687</v>
       </c>
       <c r="J75" s="0">
-        <v>0.331247699668752</v>
+        <v>0.34965034965034936</v>
       </c>
       <c r="K75" s="0">
         <v>0</v>
       </c>
       <c r="L75" s="0">
-        <v>0.48051503747706237</v>
+        <v>0.41675737878269481</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0">
-        <v>0.35443536477306259</v>
+        <v>0.22890617308260294</v>
       </c>
       <c r="B76" s="0">
-        <v>0.087719298245613961</v>
+        <v>0</v>
       </c>
       <c r="C76" s="0">
-        <v>0.27010233454646876</v>
+        <v>0.11159157483609977</v>
       </c>
       <c r="D76" s="0">
-        <v>0.20436131079748976</v>
+        <v>0.081744524318995912</v>
       </c>
       <c r="E76" s="0">
-        <v>0.22375369193591677</v>
+        <v>0.22435036844774583</v>
       </c>
       <c r="F76" s="0">
-        <v>0.37841574791689375</v>
+        <v>0.33839100534876077</v>
       </c>
       <c r="G76" s="0">
-        <v>0.26151679742506517</v>
+        <v>0.16093341380004009</v>
       </c>
       <c r="H76" s="0">
-        <v>0.36925524058399106</v>
+        <v>0.28972334261205451</v>
       </c>
       <c r="I76" s="0">
-        <v>0.20257790312009671</v>
+        <v>0.21449425036245537</v>
       </c>
       <c r="J76" s="0">
-        <v>0.40485829959514136</v>
+        <v>0.22083179977916803</v>
       </c>
       <c r="K76" s="0">
         <v>0</v>
       </c>
       <c r="L76" s="0">
-        <v>0.37321556308898052</v>
+        <v>0.34833452554971511</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0">
-        <v>0.31997637097568149</v>
+        <v>0.22398345968297706</v>
       </c>
       <c r="B77" s="0">
         <v>0.087719298245613961</v>
       </c>
       <c r="C77" s="0">
-        <v>0.18387248126402803</v>
+        <v>0.078621336816343021</v>
       </c>
       <c r="D77" s="0">
-        <v>0.1346380400548168</v>
+        <v>0.076936022888466751</v>
       </c>
       <c r="E77" s="0">
-        <v>0.19809660192726497</v>
+        <v>0.18198633610787895</v>
       </c>
       <c r="F77" s="0">
-        <v>0.39297019975985126</v>
+        <v>0.30382418222173679</v>
       </c>
       <c r="G77" s="0">
-        <v>0.34198350432508523</v>
+        <v>0.18105009052504509</v>
       </c>
       <c r="H77" s="0">
-        <v>0.3351701414531611</v>
+        <v>0.26699994319150122</v>
       </c>
       <c r="I77" s="0">
-        <v>0.2005918452463703</v>
+        <v>0.19066155587773811</v>
       </c>
       <c r="J77" s="0">
-        <v>0.36805299963194671</v>
+        <v>0.18402649981597335</v>
       </c>
       <c r="K77" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L77" s="0">
-        <v>0.33122881224147016</v>
+        <v>0.32967374739526606</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0">
-        <v>0.24367431328148054</v>
+        <v>0.18952446588559599</v>
       </c>
       <c r="B78" s="0">
         <v>0.087719298245613961</v>
       </c>
       <c r="C78" s="0">
-        <v>0.1610469318657349</v>
+        <v>0.062136217806464646</v>
       </c>
       <c r="D78" s="0">
-        <v>0.13704229077008137</v>
+        <v>0.098574279325848016</v>
       </c>
       <c r="E78" s="0">
-        <v>0.17601957098958784</v>
+        <v>0.14737909842179048</v>
       </c>
       <c r="F78" s="0">
-        <v>0.30382418222173679</v>
+        <v>0.24742568133027668</v>
       </c>
       <c r="G78" s="0">
-        <v>0.18105009052504509</v>
+        <v>0.10058338362502504</v>
       </c>
       <c r="H78" s="0">
-        <v>0.27836164290177784</v>
+        <v>0.23291484406067128</v>
       </c>
       <c r="I78" s="0">
-        <v>0.15888462989811508</v>
+        <v>0.12710770391849208</v>
       </c>
       <c r="J78" s="0">
-        <v>0.34965034965034936</v>
+        <v>0.14722119985277868</v>
       </c>
       <c r="K78" s="0">
         <v>0.12886597938144317</v>
       </c>
       <c r="L78" s="0">
-        <v>0.30790283954840891</v>
+        <v>0.25503063477747001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0">
-        <v>0.22890617308260294</v>
+        <v>0.14275868858915022</v>
       </c>
       <c r="B79" s="0">
         <v>0</v>
       </c>
       <c r="C79" s="0">
-        <v>0.14582989893353948</v>
+        <v>0.039310668408171511</v>
       </c>
       <c r="D79" s="0">
-        <v>0.072127521457937577</v>
+        <v>0.091361527180054247</v>
       </c>
       <c r="E79" s="0">
-        <v>0.14081565679167027</v>
+        <v>0.12768877353142982</v>
       </c>
       <c r="F79" s="0">
-        <v>0.27107666557508253</v>
+        <v>0.16373758323327134</v>
       </c>
       <c r="G79" s="0">
-        <v>0.16093341380004009</v>
+        <v>0.10058338362502504</v>
       </c>
       <c r="H79" s="0">
-        <v>0.29540419246719279</v>
+        <v>0.16474464579901138</v>
       </c>
       <c r="I79" s="0">
-        <v>0.17080097714047374</v>
+        <v>0.12512164604476564</v>
       </c>
       <c r="J79" s="0">
-        <v>0.22083179977916803</v>
+        <v>0.27603974972396</v>
       </c>
       <c r="K79" s="0">
         <v>0.12886597938144317</v>
       </c>
       <c r="L79" s="0">
-        <v>0.27524647777812311</v>
+        <v>0.24570024570024548</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0">
-        <v>0.17967903908634425</v>
+        <v>0.11322240819139499</v>
       </c>
       <c r="B80" s="0">
-        <v>0</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C80" s="0">
-        <v>0.093838369748538444</v>
+        <v>0.027897893709024943</v>
       </c>
       <c r="D80" s="0">
-        <v>0.098574279325848016</v>
+        <v>0.055297766451085466</v>
       </c>
       <c r="E80" s="0">
-        <v>0.10322503654643626</v>
+        <v>0.092484859333512248</v>
       </c>
       <c r="F80" s="0">
-        <v>0.2383291489284283</v>
+        <v>0.14736382490994421</v>
       </c>
       <c r="G80" s="0">
-        <v>0.14081673707503506</v>
+        <v>0.080466706900020044</v>
       </c>
       <c r="H80" s="0">
-        <v>0.23859569391580959</v>
+        <v>0.1477020962335964</v>
       </c>
       <c r="I80" s="0">
-        <v>0.11121924092868056</v>
+        <v>0.10526106730750123</v>
       </c>
       <c r="J80" s="0">
-        <v>0.25763709974236265</v>
+        <v>0.20242914979757068</v>
       </c>
       <c r="K80" s="0">
-        <v>0</v>
+        <v>0.77319587628865916</v>
       </c>
       <c r="L80" s="0">
-        <v>0.24570024570024548</v>
+        <v>0.18816284639069433</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0">
-        <v>0.15014275868858901</v>
+        <v>0.098454267992517386</v>
       </c>
       <c r="B81" s="0">
-        <v>0.087719298245613961</v>
+        <v>0</v>
       </c>
       <c r="C81" s="0">
-        <v>0.096374541903904348</v>
+        <v>0.030434065864390847</v>
       </c>
       <c r="D81" s="0">
-        <v>0.10097853004111258</v>
+        <v>0.050489265020556291</v>
       </c>
       <c r="E81" s="0">
-        <v>0.092484859333512248</v>
+        <v>0.085324741191562928</v>
       </c>
       <c r="F81" s="0">
-        <v>0.14372521194920485</v>
+        <v>0.11825492122402931</v>
       </c>
       <c r="G81" s="0">
-        <v>0.22128344397505512</v>
+        <v>0.020116676725005011</v>
       </c>
       <c r="H81" s="0">
-        <v>0.21019144464011796</v>
+        <v>0.12497869681304312</v>
       </c>
       <c r="I81" s="0">
-        <v>0.09334472006514262</v>
+        <v>0.075470199201604665</v>
       </c>
       <c r="J81" s="0">
-        <v>0.12881854987118133</v>
+        <v>0.165623849834376</v>
       </c>
       <c r="K81" s="0">
-        <v>0.5154639175257727</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L81" s="0">
-        <v>0.18971791123689841</v>
+        <v>0.18349765185208206</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0">
-        <v>0.18706310918578511</v>
+        <v>0.063995274195137009</v>
       </c>
       <c r="B82" s="0">
-        <v>0.087719298245614932</v>
+        <v>0.35087719298245973</v>
       </c>
       <c r="C82" s="0">
-        <v>0.05072344310731864</v>
+        <v>0.01268086077682966</v>
       </c>
       <c r="D82" s="0">
-        <v>0.07453177217320299</v>
+        <v>0.043276512874763022</v>
       </c>
       <c r="E82" s="0">
-        <v>0.063247710253886508</v>
+        <v>0.055490915600107972</v>
       </c>
       <c r="F82" s="0">
-        <v>0.14918313139031553</v>
+        <v>0.098242549939963897</v>
       </c>
       <c r="G82" s="0">
-        <v>0.20116676725005234</v>
+        <v>0.020116676725005236</v>
       </c>
       <c r="H82" s="0">
-        <v>0.14770209623359803</v>
+        <v>0.10225529739249097</v>
       </c>
       <c r="I82" s="0">
-        <v>0.037735099600802749</v>
+        <v>0.073484141327879046</v>
       </c>
       <c r="J82" s="0">
-        <v>0.16562384983437783</v>
+        <v>0.11041589988958524</v>
       </c>
       <c r="K82" s="0">
-        <v>0.25773195876288924</v>
+        <v>1.030927835051557</v>
       </c>
       <c r="L82" s="0">
-        <v>0.14306596585077744</v>
+        <v>0.11196466892669539</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0">
-        <v>0.14522004528896315</v>
+        <v>0.046765777296445758</v>
       </c>
       <c r="B83" s="0">
-        <v>0.26315789473684187</v>
+        <v>0</v>
       </c>
       <c r="C83" s="0">
-        <v>0.04565109879658627</v>
+        <v>0.010144688621463616</v>
       </c>
       <c r="D83" s="0">
-        <v>0.072127521457937577</v>
+        <v>0.0096170028610583439</v>
       </c>
       <c r="E83" s="0">
-        <v>0.050120826993645354</v>
+        <v>0.048330797458158013</v>
       </c>
       <c r="F83" s="0">
-        <v>0.11461630826328992</v>
+        <v>0.069133646254047887</v>
       </c>
       <c r="G83" s="0">
-        <v>0.14081673707503506</v>
+        <v>0.040233353450010022</v>
       </c>
       <c r="H83" s="0">
         <v>0.12497869681304312</v>
       </c>
       <c r="I83" s="0">
-        <v>0.07149808345415179</v>
+        <v>0.053623562590613842</v>
       </c>
       <c r="J83" s="0">
-        <v>0.073610599926389339</v>
+        <v>0.03680529996319467</v>
       </c>
       <c r="K83" s="0">
-        <v>0.25773195876288635</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L83" s="0">
-        <v>0.13373557677355136</v>
+        <v>0.091748825926041028</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0">
-        <v>0.11076105149158205</v>
+        <v>0.039381707197006954</v>
       </c>
       <c r="B84" s="0">
-        <v>0</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C84" s="0">
-        <v>0.035506410175122662</v>
+        <v>0.011412774699146568</v>
       </c>
       <c r="D84" s="0">
-        <v>0.081744524318995912</v>
+        <v>0.014425504291587513</v>
       </c>
       <c r="E84" s="0">
-        <v>0.042364032339866901</v>
+        <v>0.028640472567797344</v>
       </c>
       <c r="F84" s="0">
-        <v>0.085507404577375032</v>
+        <v>0.047301968489611719</v>
       </c>
       <c r="G84" s="0">
-        <v>0.12070006035003007</v>
+        <v>0.060350030175015036</v>
       </c>
       <c r="H84" s="0">
-        <v>0.090893597682213167</v>
+        <v>0.034085099130829945</v>
       </c>
       <c r="I84" s="0">
-        <v>0.047665388969434529</v>
+        <v>0.037735099600802333</v>
       </c>
       <c r="J84" s="0">
-        <v>0.165623849834376</v>
+        <v>0.073610599926389339</v>
       </c>
       <c r="K84" s="0">
         <v>0.5154639175257727</v>
       </c>
       <c r="L84" s="0">
-        <v>0.10729947438808189</v>
+        <v>0.091748825926041028</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0">
-        <v>0.088608841193265647</v>
+        <v>0.024613566998129347</v>
       </c>
       <c r="B85" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C85" s="0">
-        <v>0.017753205087561331</v>
+        <v>0.0050723443107318078</v>
       </c>
       <c r="D85" s="0">
-        <v>0.067319020027408402</v>
+        <v>0.016829755006852101</v>
       </c>
       <c r="E85" s="0">
-        <v>0.035800590709746678</v>
+        <v>0.028640472567797344</v>
       </c>
       <c r="F85" s="0">
-        <v>0.061856420332569169</v>
+        <v>0.01273514536258777</v>
       </c>
       <c r="G85" s="0">
-        <v>0.020116676725005011</v>
+        <v>0.060350030175015036</v>
       </c>
       <c r="H85" s="0">
-        <v>0.10225529739248983</v>
+        <v>0.06248934840652156</v>
       </c>
       <c r="I85" s="0">
-        <v>0.029790868105896578</v>
+        <v>0.031776925979623019</v>
       </c>
       <c r="J85" s="0">
-        <v>0.073610599926389339</v>
+        <v>0</v>
       </c>
       <c r="K85" s="0">
-        <v>0.77319587628865916</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L85" s="0">
-        <v>0.062202593848163408</v>
+        <v>0.051317139924734814</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0">
-        <v>0.051688490696071628</v>
+        <v>0.017229496898690543</v>
       </c>
       <c r="B86" s="0">
         <v>0.26315789473684187</v>
       </c>
       <c r="C86" s="0">
-        <v>0.025361721553659039</v>
+        <v>0.0025361721553659039</v>
       </c>
       <c r="D86" s="0">
-        <v>0.052893515735820879</v>
+        <v>0.002404250715264586</v>
       </c>
       <c r="E86" s="0">
-        <v>0.022673707449506232</v>
+        <v>0.0095468241892657808</v>
       </c>
       <c r="F86" s="0">
-        <v>0.032747516646654262</v>
+        <v>0.027289597205545222</v>
       </c>
       <c r="G86" s="0">
-        <v>0.020116676725005011</v>
+        <v>0.060350030175015036</v>
       </c>
       <c r="H86" s="0">
-        <v>0.073851048116798199</v>
+        <v>0.028404249275691615</v>
       </c>
       <c r="I86" s="0">
-        <v>0.025818752358443702</v>
+        <v>0.029790868105896578</v>
       </c>
       <c r="J86" s="0">
-        <v>0.092013249907986677</v>
+        <v>0.018402649981597335</v>
       </c>
       <c r="K86" s="0">
-        <v>0.77319587628865916</v>
+        <v>1.8041237113402044</v>
       </c>
       <c r="L86" s="0">
-        <v>0.052872204770938902</v>
+        <v>0.031101296924081704</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0">
-        <v>0.054149847395884562</v>
+        <v>0.0098454267992517386</v>
       </c>
       <c r="B87" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C87" s="0">
-        <v>0.01268086077682952</v>
+        <v>0</v>
       </c>
       <c r="D87" s="0">
-        <v>0.050489265020556291</v>
+        <v>0.002404250715264586</v>
       </c>
       <c r="E87" s="0">
         <v>0.01312688326024045</v>
       </c>
       <c r="F87" s="0">
-        <v>0.01273514536258777</v>
+        <v>0.0090965324018484079</v>
       </c>
       <c r="G87" s="0">
-        <v>0</v>
+        <v>0.060350030175015036</v>
       </c>
       <c r="H87" s="0">
-        <v>0.034085099130829945</v>
+        <v>0.051127648696244914</v>
       </c>
       <c r="I87" s="0">
-        <v>0.017874520863537947</v>
+        <v>0.0099302893686321926</v>
       </c>
       <c r="J87" s="0">
-        <v>0.073610599926389339</v>
+        <v>0.018402649981597335</v>
       </c>
       <c r="K87" s="0">
-        <v>1.6752577319587614</v>
+        <v>1.5463917525773183</v>
       </c>
       <c r="L87" s="0">
-        <v>0.043541815693714389</v>
+        <v>0.02021584300065311</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0">
-        <v>0.027074923697942281</v>
+        <v>0.0073840700994388039</v>
       </c>
       <c r="B88" s="0">
-        <v>0.35087719298245584</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C88" s="0">
-        <v>0.0063404303884147598</v>
+        <v>0.001268086077682952</v>
       </c>
       <c r="D88" s="0">
-        <v>0.026446757867910439</v>
+        <v>0</v>
       </c>
       <c r="E88" s="0">
-        <v>0.0053700886064620016</v>
+        <v>0.0059667651182911136</v>
       </c>
       <c r="F88" s="0">
-        <v>0.0018193064803696812</v>
+        <v>0.0090965324018484079</v>
       </c>
       <c r="G88" s="0">
-        <v>0.080466706900020044</v>
+        <v>0</v>
       </c>
       <c r="H88" s="0">
-        <v>0.045446798841106584</v>
+        <v>0.005680849855138323</v>
       </c>
       <c r="I88" s="0">
-        <v>0.01390240511608507</v>
+        <v>0.0039721157474528774</v>
       </c>
       <c r="J88" s="0">
-        <v>0.055207949944792008</v>
+        <v>0.018402649981597335</v>
       </c>
       <c r="K88" s="0">
-        <v>1.6752577319587614</v>
+        <v>0.90206185567010222</v>
       </c>
       <c r="L88" s="0">
-        <v>0.024881037539265367</v>
+        <v>0.017105713308244938</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>0.0049227133996258693</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B89" s="0">
-        <v>0.17543859649122792</v>
+        <v>0</v>
       </c>
       <c r="C89" s="0">
-        <v>0.001268086077682952</v>
+        <v>0</v>
       </c>
       <c r="D89" s="0">
-        <v>0.019234005722116688</v>
+        <v>0.004808501430529172</v>
       </c>
       <c r="E89" s="0">
-        <v>0.007160118141949336</v>
+        <v>0.0011933530236582226</v>
       </c>
       <c r="F89" s="0">
-        <v>0.010915838882218089</v>
+        <v>0.0054579194411090446</v>
       </c>
       <c r="G89" s="0">
-        <v>0.060350030175015036</v>
+        <v>0</v>
       </c>
       <c r="H89" s="0">
-        <v>0.028404249275691615</v>
+        <v>0.005680849855138323</v>
       </c>
       <c r="I89" s="0">
-        <v>0.0059581736211793161</v>
+        <v>0.0019860578737264387</v>
       </c>
       <c r="J89" s="0">
-        <v>0.055207949944792008</v>
+        <v>0</v>
       </c>
       <c r="K89" s="0">
-        <v>1.2886597938144317</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L89" s="0">
-        <v>0.0093303890772245112</v>
+        <v>0.007775324231020426</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>0.014768140198877608</v>
+        <v>0</v>
       </c>
       <c r="B90" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C90" s="0">
-        <v>0.001268086077682952</v>
+        <v>0</v>
       </c>
       <c r="D90" s="0">
-        <v>0.012021253576322928</v>
+        <v>0</v>
       </c>
       <c r="E90" s="0">
-        <v>0.001790029535487334</v>
+        <v>0.0023867060473164452</v>
       </c>
       <c r="F90" s="0">
-        <v>0.0090965324018484079</v>
+        <v>0.0018193064803696812</v>
       </c>
       <c r="G90" s="0">
-        <v>0.020116676725005011</v>
+        <v>0</v>
       </c>
       <c r="H90" s="0">
-        <v>0.011361699710276646</v>
+        <v>0.005680849855138323</v>
       </c>
       <c r="I90" s="0">
-        <v>0.0019860578737264387</v>
+        <v>0</v>
       </c>
       <c r="J90" s="0">
         <v>0</v>
       </c>
       <c r="K90" s="0">
-        <v>0.64432989690721587</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L90" s="0">
-        <v>0.010885453923428597</v>
+        <v>0.0015550648462040854</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>0.0073840700994388039</v>
+        <v>0</v>
       </c>
       <c r="B91" s="0">
-        <v>0</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C91" s="0">
-        <v>0.0025361721553659039</v>
+        <v>0</v>
       </c>
       <c r="D91" s="0">
         <v>0</v>
       </c>
       <c r="E91" s="0">
-        <v>0.001790029535487334</v>
+        <v>0.0005966765118291113</v>
       </c>
       <c r="F91" s="0">
         <v>0</v>
@@ -3519,51 +3520,51 @@
         <v>0</v>
       </c>
       <c r="J91" s="0">
-        <v>0.03680529996319467</v>
+        <v>0</v>
       </c>
       <c r="K91" s="0">
-        <v>0.64432989690721587</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L91" s="0">
-        <v>0.0046651945386122556</v>
+        <v>0.0015550648462040854</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0</v>
       </c>
       <c r="B92" s="0">
         <v>0.087719298245613961</v>
       </c>
       <c r="C92" s="0">
-        <v>0.0025361721553659039</v>
+        <v>0</v>
       </c>
       <c r="D92" s="0">
-        <v>0.004808501430529172</v>
+        <v>0</v>
       </c>
       <c r="E92" s="0">
         <v>0</v>
       </c>
       <c r="F92" s="0">
-        <v>0.0018193064803696812</v>
+        <v>0</v>
       </c>
       <c r="G92" s="0">
         <v>0</v>
       </c>
       <c r="H92" s="0">
-        <v>0.005680849855138323</v>
+        <v>0</v>
       </c>
       <c r="I92" s="0">
-        <v>0.0019860578737264387</v>
+        <v>0</v>
       </c>
       <c r="J92" s="0">
-        <v>0.018402649981597335</v>
+        <v>0</v>
       </c>
       <c r="K92" s="0">
         <v>0.12886597938144317</v>
       </c>
       <c r="L92" s="0">
-        <v>0</v>
+        <v>0.0031101296924081708</v>
       </c>
     </row>
     <row r="93">
@@ -3571,7 +3572,7 @@
         <v>0</v>
       </c>
       <c r="B93" s="0">
-        <v>0.26315789473684187</v>
+        <v>0</v>
       </c>
       <c r="C93" s="0">
         <v>0</v>
@@ -3583,25 +3584,25 @@
         <v>0</v>
       </c>
       <c r="F93" s="0">
-        <v>0.0018193064803696812</v>
+        <v>0</v>
       </c>
       <c r="G93" s="0">
-        <v>0.020116676725005011</v>
+        <v>0</v>
       </c>
       <c r="H93" s="0">
         <v>0</v>
       </c>
       <c r="I93" s="0">
-        <v>0.0019860578737264387</v>
+        <v>0</v>
       </c>
       <c r="J93" s="0">
         <v>0</v>
       </c>
       <c r="K93" s="0">
-        <v>0.25773195876288635</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L93" s="0">
-        <v>0</v>
+        <v>0.0015550648462040854</v>
       </c>
     </row>
     <row r="94">
@@ -3609,7 +3610,7 @@
         <v>0</v>
       </c>
       <c r="B94" s="0">
-        <v>0.17543859649122986</v>
+        <v>0</v>
       </c>
       <c r="C94" s="0">
         <v>0</v>
@@ -3618,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="E94" s="0">
-        <v>0.00059667651182911791</v>
+        <v>0</v>
       </c>
       <c r="F94" s="0">
         <v>0</v>
@@ -3636,7 +3637,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="0">
-        <v>0.12886597938144462</v>
+        <v>0</v>
       </c>
       <c r="L94" s="0">
         <v>0</v>
@@ -3644,7 +3645,7 @@
     </row>
     <row r="95">
       <c r="A95" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0</v>
       </c>
       <c r="B95" s="0">
         <v>0</v>
@@ -3674,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="K95" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L95" s="0">
         <v>0</v>

--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0010_ses-01_WMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0010_ses-01_WMprob_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
